--- a/data/workshop.xlsx
+++ b/data/workshop.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8869" uniqueCount="3744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8937" uniqueCount="3761">
   <si>
     <t>id</t>
   </si>
@@ -10067,21 +10067,27 @@
     <t>Assemble: CV 2EA</t>
   </si>
   <si>
+    <t>2026-08-13T03:13:58.520Z</t>
+  </si>
+  <si>
     <t>033a6b1b-8daf-46cc-a1e1-292ad2451d5f</t>
   </si>
   <si>
     <t>Assemble: Pump, Lines, &amp; Screen</t>
   </si>
   <si>
+    <t>2026-08-13T11:13:08.442Z</t>
+  </si>
+  <si>
+    <t>f52cc000-4714-474d-a6c4-a3f41408fbb7</t>
+  </si>
+  <si>
+    <t>Test Bench &amp; Completed: Set up</t>
+  </si>
+  <si>
     <t>pending</t>
   </si>
   <si>
-    <t>f52cc000-4714-474d-a6c4-a3f41408fbb7</t>
-  </si>
-  <si>
-    <t>Test Bench &amp; Completed: Set up</t>
-  </si>
-  <si>
     <t>a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9</t>
   </si>
   <si>
@@ -10664,6 +10670,33 @@
     <t>Assemble: CV 2EA · oleh foreman (foreman)</t>
   </si>
   <si>
+    <t>3f198a0a-b3f2-4005-b021-dab5028198e1</t>
+  </si>
+  <si>
+    <t>Assemble: CV 2EA · oleh Administrator (superuser)</t>
+  </si>
+  <si>
+    <t>2026-08-13T03:13:58.521Z</t>
+  </si>
+  <si>
+    <t>6c2b0726-6fc6-44d8-892d-18a649e42557</t>
+  </si>
+  <si>
+    <t>Assemble: Pump, Lines, &amp; Screen · oleh Administrator (superuser)</t>
+  </si>
+  <si>
+    <t>2026-08-13T03:14:06.385Z</t>
+  </si>
+  <si>
+    <t>9755f0a1-2d88-488f-8df6-01613560c79e</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:13:02.526Z</t>
+  </si>
+  <si>
+    <t>9e3b6d6d-fd17-43f0-aa4c-a1a45607e736</t>
+  </si>
+  <si>
     <t>at</t>
   </si>
   <si>
@@ -11259,6 +11292,24 @@
   </si>
   <si>
     <t>acdf2414-7577-4d51-a4ad-bf2e00dad498</t>
+  </si>
+  <si>
+    <t>c3add70c-9f8c-4e6e-8cee-107683006c38</t>
+  </si>
+  <si>
+    <t>2026-08-13T03:13:58.523Z</t>
+  </si>
+  <si>
+    <t>69dfab07-397e-4b4e-8d2a-754b8d119909</t>
+  </si>
+  <si>
+    <t>7ff56432-97d5-4ca1-8471-db811b60b710</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:13:02.527Z</t>
+  </si>
+  <si>
+    <t>844814fb-1232-4ee7-9559-16d81e5e2860</t>
   </si>
 </sst>
 </file>
@@ -15541,7 +15592,7 @@
         <v>19</v>
       </c>
       <c r="M2">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="N2">
         <v>5340</v>
@@ -16046,16 +16097,16 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>3293</v>
+        <v>602</v>
       </c>
       <c r="F11" t="s">
         <v>3343</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>3346</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>64100</v>
       </c>
       <c r="I11">
         <v>300</v>
@@ -16063,28 +16114,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="B12" t="s">
         <v>3096</v>
       </c>
       <c r="C12" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>3348</v>
+        <v>3293</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>3349</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>28736</v>
       </c>
       <c r="I12">
         <v>300</v>
@@ -16092,19 +16143,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="B13" t="s">
         <v>3096</v>
       </c>
       <c r="C13" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -16121,19 +16172,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3351</v>
+        <v>3353</v>
       </c>
       <c r="B14" t="s">
         <v>3096</v>
       </c>
       <c r="C14" t="s">
-        <v>3352</v>
+        <v>3354</v>
       </c>
       <c r="D14">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -16150,19 +16201,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3353</v>
+        <v>3355</v>
       </c>
       <c r="B15" t="s">
         <v>3096</v>
       </c>
       <c r="C15" t="s">
-        <v>3354</v>
+        <v>3356</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -16179,19 +16230,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3355</v>
+        <v>3357</v>
       </c>
       <c r="B16" t="s">
         <v>3096</v>
       </c>
       <c r="C16" t="s">
-        <v>3356</v>
+        <v>3358</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -16208,13 +16259,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3357</v>
+        <v>3359</v>
       </c>
       <c r="B17" t="s">
         <v>3094</v>
       </c>
       <c r="C17" t="s">
-        <v>3358</v>
+        <v>3360</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -16226,7 +16277,7 @@
         <v>3301</v>
       </c>
       <c r="G17" t="s">
-        <v>3359</v>
+        <v>3361</v>
       </c>
       <c r="H17">
         <v>43</v>
@@ -16237,13 +16288,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3360</v>
+        <v>3362</v>
       </c>
       <c r="B18" t="s">
         <v>3094</v>
       </c>
       <c r="C18" t="s">
-        <v>3361</v>
+        <v>3363</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -16252,10 +16303,10 @@
         <v>602</v>
       </c>
       <c r="F18" t="s">
-        <v>3362</v>
+        <v>3364</v>
       </c>
       <c r="G18" t="s">
-        <v>3363</v>
+        <v>3365</v>
       </c>
       <c r="H18">
         <v>33</v>
@@ -16266,13 +16317,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3364</v>
+        <v>3366</v>
       </c>
       <c r="B19" t="s">
         <v>3094</v>
       </c>
       <c r="C19" t="s">
-        <v>3365</v>
+        <v>3367</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -16281,10 +16332,10 @@
         <v>602</v>
       </c>
       <c r="F19" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="G19" t="s">
-        <v>3367</v>
+        <v>3369</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -16295,13 +16346,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3368</v>
+        <v>3370</v>
       </c>
       <c r="B20" t="s">
         <v>3094</v>
       </c>
       <c r="C20" t="s">
-        <v>3369</v>
+        <v>3371</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -16310,10 +16361,10 @@
         <v>602</v>
       </c>
       <c r="F20" t="s">
-        <v>3362</v>
+        <v>3364</v>
       </c>
       <c r="G20" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="H20">
         <v>35</v>
@@ -16324,13 +16375,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3370</v>
+        <v>3372</v>
       </c>
       <c r="B21" t="s">
         <v>3094</v>
       </c>
       <c r="C21" t="s">
-        <v>3371</v>
+        <v>3373</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -16339,10 +16390,10 @@
         <v>602</v>
       </c>
       <c r="F21" t="s">
-        <v>3367</v>
+        <v>3369</v>
       </c>
       <c r="G21" t="s">
-        <v>3372</v>
+        <v>3374</v>
       </c>
       <c r="H21">
         <v>6373</v>
@@ -16353,13 +16404,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3373</v>
+        <v>3375</v>
       </c>
       <c r="B22" t="s">
         <v>3094</v>
       </c>
       <c r="C22" t="s">
-        <v>3374</v>
+        <v>3376</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -16368,10 +16419,10 @@
         <v>602</v>
       </c>
       <c r="F22" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
       <c r="G22" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="H22">
         <v>69782</v>
@@ -16382,13 +16433,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3377</v>
+        <v>3379</v>
       </c>
       <c r="B23" t="s">
         <v>3094</v>
       </c>
       <c r="C23" t="s">
-        <v>3378</v>
+        <v>3380</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -16397,10 +16448,10 @@
         <v>602</v>
       </c>
       <c r="F23" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="G23" t="s">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="H23">
         <v>12</v>
@@ -16411,13 +16462,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3380</v>
+        <v>3382</v>
       </c>
       <c r="B24" t="s">
         <v>3094</v>
       </c>
       <c r="C24" t="s">
-        <v>3381</v>
+        <v>3383</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -16426,10 +16477,10 @@
         <v>602</v>
       </c>
       <c r="F24" t="s">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="G24" t="s">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="H24">
         <v>35663</v>
@@ -16440,13 +16491,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3383</v>
+        <v>3385</v>
       </c>
       <c r="B25" t="s">
         <v>3094</v>
       </c>
       <c r="C25" t="s">
-        <v>3384</v>
+        <v>3386</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -16455,10 +16506,10 @@
         <v>602</v>
       </c>
       <c r="F25" t="s">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="G25" t="s">
-        <v>3385</v>
+        <v>3387</v>
       </c>
       <c r="H25">
         <v>30291</v>
@@ -16469,7 +16520,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3386</v>
+        <v>3388</v>
       </c>
       <c r="B26" t="s">
         <v>3094</v>
@@ -16484,10 +16535,10 @@
         <v>602</v>
       </c>
       <c r="F26" t="s">
-        <v>3385</v>
+        <v>3387</v>
       </c>
       <c r="G26" t="s">
-        <v>3387</v>
+        <v>3389</v>
       </c>
       <c r="H26">
         <v>12032</v>
@@ -16498,13 +16549,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3388</v>
+        <v>3390</v>
       </c>
       <c r="B27" t="s">
         <v>3094</v>
       </c>
       <c r="C27" t="s">
-        <v>3389</v>
+        <v>3391</v>
       </c>
       <c r="D27">
         <v>11</v>
@@ -16513,7 +16564,7 @@
         <v>3293</v>
       </c>
       <c r="F27" t="s">
-        <v>3387</v>
+        <v>3389</v>
       </c>
       <c r="G27" t="s">
         <v>19</v>
@@ -16527,19 +16578,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3390</v>
+        <v>3392</v>
       </c>
       <c r="B28" t="s">
         <v>3094</v>
       </c>
       <c r="C28" t="s">
-        <v>3391</v>
+        <v>3393</v>
       </c>
       <c r="D28">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -16556,19 +16607,19 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3392</v>
+        <v>3394</v>
       </c>
       <c r="B29" t="s">
         <v>3094</v>
       </c>
       <c r="C29" t="s">
-        <v>3393</v>
+        <v>3395</v>
       </c>
       <c r="D29">
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F29" t="s">
         <v>19</v>
@@ -16585,19 +16636,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3394</v>
+        <v>3396</v>
       </c>
       <c r="B30" t="s">
         <v>3094</v>
       </c>
       <c r="C30" t="s">
-        <v>3395</v>
+        <v>3397</v>
       </c>
       <c r="D30">
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -16614,19 +16665,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3396</v>
+        <v>3398</v>
       </c>
       <c r="B31" t="s">
         <v>3094</v>
       </c>
       <c r="C31" t="s">
-        <v>3397</v>
+        <v>3399</v>
       </c>
       <c r="D31">
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F31" t="s">
         <v>19</v>
@@ -16643,19 +16694,19 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3398</v>
+        <v>3400</v>
       </c>
       <c r="B32" t="s">
         <v>3094</v>
       </c>
       <c r="C32" t="s">
-        <v>3399</v>
+        <v>3401</v>
       </c>
       <c r="D32">
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -16672,19 +16723,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3400</v>
+        <v>3402</v>
       </c>
       <c r="B33" t="s">
         <v>3094</v>
       </c>
       <c r="C33" t="s">
-        <v>3401</v>
+        <v>3403</v>
       </c>
       <c r="D33">
         <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
@@ -16701,19 +16752,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3402</v>
+        <v>3404</v>
       </c>
       <c r="B34" t="s">
         <v>3094</v>
       </c>
       <c r="C34" t="s">
-        <v>3403</v>
+        <v>3405</v>
       </c>
       <c r="D34">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -16730,19 +16781,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3404</v>
+        <v>3406</v>
       </c>
       <c r="B35" t="s">
         <v>3094</v>
       </c>
       <c r="C35" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="D35">
         <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -16759,19 +16810,19 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3405</v>
+        <v>3407</v>
       </c>
       <c r="B36" t="s">
         <v>3094</v>
       </c>
       <c r="C36" t="s">
-        <v>3352</v>
+        <v>3354</v>
       </c>
       <c r="D36">
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -16788,19 +16839,19 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3406</v>
+        <v>3408</v>
       </c>
       <c r="B37" t="s">
         <v>3094</v>
       </c>
       <c r="C37" t="s">
-        <v>3354</v>
+        <v>3356</v>
       </c>
       <c r="D37">
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -16817,19 +16868,19 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3407</v>
+        <v>3409</v>
       </c>
       <c r="B38" t="s">
         <v>3094</v>
       </c>
       <c r="C38" t="s">
-        <v>3356</v>
+        <v>3358</v>
       </c>
       <c r="D38">
         <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F38" t="s">
         <v>19</v>
@@ -16846,7 +16897,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3408</v>
+        <v>3410</v>
       </c>
       <c r="B39" t="s">
         <v>3092</v>
@@ -16864,7 +16915,7 @@
         <v>3303</v>
       </c>
       <c r="G39" t="s">
-        <v>3409</v>
+        <v>3411</v>
       </c>
       <c r="H39">
         <v>66035</v>
@@ -16875,7 +16926,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3410</v>
+        <v>3412</v>
       </c>
       <c r="B40" t="s">
         <v>3092</v>
@@ -16890,10 +16941,10 @@
         <v>602</v>
       </c>
       <c r="F40" t="s">
-        <v>3411</v>
+        <v>3413</v>
       </c>
       <c r="G40" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
       <c r="H40">
         <v>65999</v>
@@ -16904,7 +16955,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3413</v>
+        <v>3415</v>
       </c>
       <c r="B41" t="s">
         <v>3092</v>
@@ -16919,10 +16970,10 @@
         <v>602</v>
       </c>
       <c r="F41" t="s">
-        <v>3411</v>
+        <v>3413</v>
       </c>
       <c r="G41" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
       <c r="H41">
         <v>66018</v>
@@ -16933,7 +16984,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3415</v>
+        <v>3417</v>
       </c>
       <c r="B42" t="s">
         <v>3092</v>
@@ -16948,7 +16999,7 @@
         <v>3293</v>
       </c>
       <c r="F42" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
       <c r="G42" t="s">
         <v>19</v>
@@ -16962,7 +17013,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3416</v>
+        <v>3418</v>
       </c>
       <c r="B43" t="s">
         <v>3092</v>
@@ -16974,7 +17025,7 @@
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F43" t="s">
         <v>19</v>
@@ -16991,7 +17042,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3417</v>
+        <v>3419</v>
       </c>
       <c r="B44" t="s">
         <v>3092</v>
@@ -17003,7 +17054,7 @@
         <v>6</v>
       </c>
       <c r="E44" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F44" t="s">
         <v>19</v>
@@ -17020,7 +17071,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3418</v>
+        <v>3420</v>
       </c>
       <c r="B45" t="s">
         <v>3092</v>
@@ -17032,7 +17083,7 @@
         <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F45" t="s">
         <v>19</v>
@@ -17049,7 +17100,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3419</v>
+        <v>3421</v>
       </c>
       <c r="B46" t="s">
         <v>3092</v>
@@ -17061,7 +17112,7 @@
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
@@ -17078,7 +17129,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3420</v>
+        <v>3422</v>
       </c>
       <c r="B47" t="s">
         <v>3092</v>
@@ -17090,7 +17141,7 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -17107,7 +17158,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3421</v>
+        <v>3423</v>
       </c>
       <c r="B48" t="s">
         <v>3092</v>
@@ -17119,7 +17170,7 @@
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -17136,19 +17187,19 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3422</v>
+        <v>3424</v>
       </c>
       <c r="B49" t="s">
         <v>3092</v>
       </c>
       <c r="C49" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="D49">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -17165,19 +17216,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3423</v>
+        <v>3425</v>
       </c>
       <c r="B50" t="s">
         <v>3092</v>
       </c>
       <c r="C50" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="D50">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -17194,19 +17245,19 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3424</v>
+        <v>3426</v>
       </c>
       <c r="B51" t="s">
         <v>3092</v>
       </c>
       <c r="C51" t="s">
-        <v>3352</v>
+        <v>3354</v>
       </c>
       <c r="D51">
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F51" t="s">
         <v>19</v>
@@ -17223,19 +17274,19 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="B52" t="s">
         <v>3092</v>
       </c>
       <c r="C52" t="s">
-        <v>3354</v>
+        <v>3356</v>
       </c>
       <c r="D52">
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F52" t="s">
         <v>19</v>
@@ -17252,19 +17303,19 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3426</v>
+        <v>3428</v>
       </c>
       <c r="B53" t="s">
         <v>3092</v>
       </c>
       <c r="C53" t="s">
-        <v>3356</v>
+        <v>3358</v>
       </c>
       <c r="D53">
         <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="F53" t="s">
         <v>19</v>
@@ -17287,7 +17338,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17298,7 +17349,7 @@
         <v>599</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>3427</v>
+        <v>3429</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>10</v>
@@ -17313,21 +17364,21 @@
         <v>604</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>3428</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3429</v>
+        <v>3431</v>
       </c>
       <c r="B2" t="s">
         <v>3096</v>
       </c>
       <c r="C2" t="s">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="D2" t="s">
-        <v>3431</v>
+        <v>3433</v>
       </c>
       <c r="E2" t="s">
         <v>3295</v>
@@ -17344,19 +17395,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3432</v>
+        <v>3434</v>
       </c>
       <c r="B3" t="s">
         <v>3096</v>
       </c>
       <c r="C3" t="s">
-        <v>3433</v>
+        <v>3435</v>
       </c>
       <c r="D3" t="s">
-        <v>3434</v>
+        <v>3436</v>
       </c>
       <c r="E3" t="s">
-        <v>3435</v>
+        <v>3437</v>
       </c>
       <c r="F3" t="s">
         <v>3066</v>
@@ -17370,16 +17421,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3436</v>
+        <v>3438</v>
       </c>
       <c r="B4" t="s">
         <v>3096</v>
       </c>
       <c r="C4" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D4" t="s">
-        <v>3438</v>
+        <v>3440</v>
       </c>
       <c r="E4" t="s">
         <v>3296</v>
@@ -17396,16 +17447,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3439</v>
+        <v>3441</v>
       </c>
       <c r="B5" t="s">
         <v>3096</v>
       </c>
       <c r="C5" t="s">
-        <v>3440</v>
+        <v>3442</v>
       </c>
       <c r="D5" t="s">
-        <v>3441</v>
+        <v>3443</v>
       </c>
       <c r="E5" t="s">
         <v>3296</v>
@@ -17422,19 +17473,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3442</v>
+        <v>3444</v>
       </c>
       <c r="B6" t="s">
         <v>3096</v>
       </c>
       <c r="C6" t="s">
-        <v>3443</v>
+        <v>3445</v>
       </c>
       <c r="D6" t="s">
-        <v>3444</v>
+        <v>3446</v>
       </c>
       <c r="E6" t="s">
-        <v>3445</v>
+        <v>3447</v>
       </c>
       <c r="F6" t="s">
         <v>3066</v>
@@ -17448,16 +17499,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3446</v>
+        <v>3448</v>
       </c>
       <c r="B7" t="s">
         <v>3096</v>
       </c>
       <c r="C7" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D7" t="s">
-        <v>3438</v>
+        <v>3440</v>
       </c>
       <c r="E7" t="s">
         <v>3317</v>
@@ -17474,16 +17525,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3448</v>
+        <v>3450</v>
       </c>
       <c r="B8" t="s">
         <v>3096</v>
       </c>
       <c r="C8" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D8" t="s">
-        <v>3449</v>
+        <v>3451</v>
       </c>
       <c r="E8" t="s">
         <v>3317</v>
@@ -17500,19 +17551,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3450</v>
+        <v>3452</v>
       </c>
       <c r="B9" t="s">
         <v>3096</v>
       </c>
       <c r="C9" t="s">
-        <v>3451</v>
+        <v>3453</v>
       </c>
       <c r="D9" t="s">
-        <v>3452</v>
+        <v>3454</v>
       </c>
       <c r="E9" t="s">
-        <v>3453</v>
+        <v>3455</v>
       </c>
       <c r="F9" t="s">
         <v>3080</v>
@@ -17526,16 +17577,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3454</v>
+        <v>3456</v>
       </c>
       <c r="B10" t="s">
         <v>3096</v>
       </c>
       <c r="C10" t="s">
-        <v>3455</v>
+        <v>3457</v>
       </c>
       <c r="D10" t="s">
-        <v>3456</v>
+        <v>3458</v>
       </c>
       <c r="E10" t="s">
         <v>3320</v>
@@ -17552,16 +17603,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3457</v>
+        <v>3459</v>
       </c>
       <c r="B11" t="s">
         <v>3096</v>
       </c>
       <c r="C11" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D11" t="s">
-        <v>3458</v>
+        <v>3460</v>
       </c>
       <c r="E11" t="s">
         <v>3321</v>
@@ -17578,16 +17629,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3459</v>
+        <v>3461</v>
       </c>
       <c r="B12" t="s">
         <v>3096</v>
       </c>
       <c r="C12" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D12" t="s">
-        <v>3460</v>
+        <v>3462</v>
       </c>
       <c r="E12" t="s">
         <v>3321</v>
@@ -17604,16 +17655,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3461</v>
+        <v>3463</v>
       </c>
       <c r="B13" t="s">
         <v>3094</v>
       </c>
       <c r="C13" t="s">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="D13" t="s">
-        <v>3462</v>
+        <v>3464</v>
       </c>
       <c r="E13" t="s">
         <v>3300</v>
@@ -17630,16 +17681,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3463</v>
+        <v>3465</v>
       </c>
       <c r="B14" t="s">
         <v>3094</v>
       </c>
       <c r="C14" t="s">
-        <v>3433</v>
+        <v>3435</v>
       </c>
       <c r="D14" t="s">
-        <v>3464</v>
+        <v>3466</v>
       </c>
       <c r="E14" t="s">
         <v>3307</v>
@@ -17656,16 +17707,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3465</v>
+        <v>3467</v>
       </c>
       <c r="B15" t="s">
         <v>3094</v>
       </c>
       <c r="C15" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D15" t="s">
-        <v>3466</v>
+        <v>3468</v>
       </c>
       <c r="E15" t="s">
         <v>3301</v>
@@ -17682,16 +17733,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3467</v>
+        <v>3469</v>
       </c>
       <c r="B16" t="s">
         <v>3094</v>
       </c>
       <c r="C16" t="s">
-        <v>3440</v>
+        <v>3442</v>
       </c>
       <c r="D16" t="s">
-        <v>3468</v>
+        <v>3470</v>
       </c>
       <c r="E16" t="s">
         <v>3301</v>
@@ -17708,19 +17759,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3469</v>
+        <v>3471</v>
       </c>
       <c r="B17" t="s">
         <v>3094</v>
       </c>
       <c r="C17" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D17" t="s">
-        <v>3470</v>
+        <v>3472</v>
       </c>
       <c r="E17" t="s">
-        <v>3362</v>
+        <v>3364</v>
       </c>
       <c r="F17" t="s">
         <v>3080</v>
@@ -17734,19 +17785,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3471</v>
+        <v>3473</v>
       </c>
       <c r="B18" t="s">
         <v>3094</v>
       </c>
       <c r="C18" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D18" t="s">
-        <v>3466</v>
+        <v>3468</v>
       </c>
       <c r="E18" t="s">
-        <v>3359</v>
+        <v>3361</v>
       </c>
       <c r="F18" t="s">
         <v>3080</v>
@@ -17760,19 +17811,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3472</v>
+        <v>3474</v>
       </c>
       <c r="B19" t="s">
         <v>3094</v>
       </c>
       <c r="C19" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D19" t="s">
-        <v>3473</v>
+        <v>3475</v>
       </c>
       <c r="E19" t="s">
-        <v>3363</v>
+        <v>3365</v>
       </c>
       <c r="F19" t="s">
         <v>3080</v>
@@ -17786,19 +17837,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3474</v>
+        <v>3476</v>
       </c>
       <c r="B20" t="s">
         <v>3094</v>
       </c>
       <c r="C20" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D20" t="s">
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="E20" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="F20" t="s">
         <v>3080</v>
@@ -17812,19 +17863,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3476</v>
+        <v>3478</v>
       </c>
       <c r="B21" t="s">
         <v>3094</v>
       </c>
       <c r="C21" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D21" t="s">
-        <v>3477</v>
+        <v>3479</v>
       </c>
       <c r="E21" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="F21" t="s">
         <v>3080</v>
@@ -17838,19 +17889,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3478</v>
+        <v>3480</v>
       </c>
       <c r="B22" t="s">
         <v>3094</v>
       </c>
       <c r="C22" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D22" t="s">
-        <v>3477</v>
+        <v>3479</v>
       </c>
       <c r="E22" t="s">
-        <v>3367</v>
+        <v>3369</v>
       </c>
       <c r="F22" t="s">
         <v>3080</v>
@@ -17864,19 +17915,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3479</v>
+        <v>3481</v>
       </c>
       <c r="B23" t="s">
         <v>3094</v>
       </c>
       <c r="C23" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D23" t="s">
-        <v>3480</v>
+        <v>3482</v>
       </c>
       <c r="E23" t="s">
-        <v>3367</v>
+        <v>3369</v>
       </c>
       <c r="F23" t="s">
         <v>3080</v>
@@ -17890,16 +17941,16 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3481</v>
+        <v>3483</v>
       </c>
       <c r="B24" t="s">
         <v>3096</v>
       </c>
       <c r="C24" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D24" t="s">
-        <v>3460</v>
+        <v>3462</v>
       </c>
       <c r="E24" t="s">
         <v>3324</v>
@@ -17916,16 +17967,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3482</v>
+        <v>3484</v>
       </c>
       <c r="B25" t="s">
         <v>3096</v>
       </c>
       <c r="C25" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D25" t="s">
-        <v>3483</v>
+        <v>3485</v>
       </c>
       <c r="E25" t="s">
         <v>3324</v>
@@ -17942,19 +17993,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3484</v>
+        <v>3486</v>
       </c>
       <c r="B26" t="s">
         <v>3094</v>
       </c>
       <c r="C26" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D26" t="s">
-        <v>3480</v>
+        <v>3482</v>
       </c>
       <c r="E26" t="s">
-        <v>3372</v>
+        <v>3374</v>
       </c>
       <c r="F26" t="s">
         <v>3080</v>
@@ -17968,19 +18019,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3485</v>
+        <v>3487</v>
       </c>
       <c r="B27" t="s">
         <v>3094</v>
       </c>
       <c r="C27" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D27" t="s">
-        <v>3486</v>
+        <v>3488</v>
       </c>
       <c r="E27" t="s">
-        <v>3487</v>
+        <v>3489</v>
       </c>
       <c r="F27" t="s">
         <v>3080</v>
@@ -17994,16 +18045,16 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3488</v>
+        <v>3490</v>
       </c>
       <c r="B28" t="s">
         <v>3092</v>
       </c>
       <c r="C28" t="s">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="D28" t="s">
-        <v>3431</v>
+        <v>3433</v>
       </c>
       <c r="E28" t="s">
         <v>3302</v>
@@ -18020,16 +18071,16 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3489</v>
+        <v>3491</v>
       </c>
       <c r="B29" t="s">
         <v>3092</v>
       </c>
       <c r="C29" t="s">
-        <v>3433</v>
+        <v>3435</v>
       </c>
       <c r="D29" t="s">
-        <v>3490</v>
+        <v>3492</v>
       </c>
       <c r="E29" t="s">
         <v>3309</v>
@@ -18046,16 +18097,16 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3491</v>
+        <v>3493</v>
       </c>
       <c r="B30" t="s">
         <v>3092</v>
       </c>
       <c r="C30" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D30" t="s">
-        <v>3438</v>
+        <v>3440</v>
       </c>
       <c r="E30" t="s">
         <v>3303</v>
@@ -18072,16 +18123,16 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3492</v>
+        <v>3494</v>
       </c>
       <c r="B31" t="s">
         <v>3092</v>
       </c>
       <c r="C31" t="s">
-        <v>3440</v>
+        <v>3442</v>
       </c>
       <c r="D31" t="s">
-        <v>3441</v>
+        <v>3443</v>
       </c>
       <c r="E31" t="s">
         <v>3303</v>
@@ -18098,19 +18149,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3493</v>
+        <v>3495</v>
       </c>
       <c r="B32" t="s">
         <v>3092</v>
       </c>
       <c r="C32" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D32" t="s">
-        <v>3494</v>
+        <v>3496</v>
       </c>
       <c r="E32" t="s">
-        <v>3411</v>
+        <v>3413</v>
       </c>
       <c r="F32" t="s">
         <v>3066</v>
@@ -18124,19 +18175,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3495</v>
+        <v>3497</v>
       </c>
       <c r="B33" t="s">
         <v>3094</v>
       </c>
       <c r="C33" t="s">
-        <v>3451</v>
+        <v>3453</v>
       </c>
       <c r="D33" t="s">
-        <v>3496</v>
+        <v>3498</v>
       </c>
       <c r="E33" t="s">
-        <v>3497</v>
+        <v>3499</v>
       </c>
       <c r="F33" t="s">
         <v>3066</v>
@@ -18150,19 +18201,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3498</v>
+        <v>3500</v>
       </c>
       <c r="B34" t="s">
         <v>3094</v>
       </c>
       <c r="C34" t="s">
-        <v>3455</v>
+        <v>3457</v>
       </c>
       <c r="D34" t="s">
-        <v>3499</v>
+        <v>3501</v>
       </c>
       <c r="E34" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
       <c r="F34" t="s">
         <v>3066</v>
@@ -18176,19 +18227,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3500</v>
+        <v>3502</v>
       </c>
       <c r="B35" t="s">
         <v>3094</v>
       </c>
       <c r="C35" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D35" t="s">
-        <v>3501</v>
+        <v>3503</v>
       </c>
       <c r="E35" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="F35" t="s">
         <v>3066</v>
@@ -18202,19 +18253,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3502</v>
+        <v>3504</v>
       </c>
       <c r="B36" t="s">
         <v>3094</v>
       </c>
       <c r="C36" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D36" t="s">
-        <v>3503</v>
+        <v>3505</v>
       </c>
       <c r="E36" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="F36" t="s">
         <v>3066</v>
@@ -18228,19 +18279,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3504</v>
+        <v>3506</v>
       </c>
       <c r="B37" t="s">
         <v>3094</v>
       </c>
       <c r="C37" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D37" t="s">
-        <v>3503</v>
+        <v>3505</v>
       </c>
       <c r="E37" t="s">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="F37" t="s">
         <v>3066</v>
@@ -18254,19 +18305,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3505</v>
+        <v>3507</v>
       </c>
       <c r="B38" t="s">
         <v>3094</v>
       </c>
       <c r="C38" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D38" t="s">
-        <v>3506</v>
+        <v>3508</v>
       </c>
       <c r="E38" t="s">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="F38" t="s">
         <v>3066</v>
@@ -18280,16 +18331,16 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3507</v>
+        <v>3509</v>
       </c>
       <c r="B39" t="s">
         <v>3096</v>
       </c>
       <c r="C39" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D39" t="s">
-        <v>3508</v>
+        <v>3510</v>
       </c>
       <c r="E39" t="s">
         <v>3327</v>
@@ -18306,16 +18357,16 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3509</v>
+        <v>3511</v>
       </c>
       <c r="B40" t="s">
         <v>3096</v>
       </c>
       <c r="C40" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D40" t="s">
-        <v>3510</v>
+        <v>3512</v>
       </c>
       <c r="E40" t="s">
         <v>3327</v>
@@ -18332,16 +18383,16 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3511</v>
+        <v>3513</v>
       </c>
       <c r="B41" t="s">
         <v>3096</v>
       </c>
       <c r="C41" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D41" t="s">
-        <v>3510</v>
+        <v>3512</v>
       </c>
       <c r="E41" t="s">
         <v>3330</v>
@@ -18358,16 +18409,16 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3512</v>
+        <v>3514</v>
       </c>
       <c r="B42" t="s">
         <v>3096</v>
       </c>
       <c r="C42" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D42" t="s">
-        <v>3513</v>
+        <v>3515</v>
       </c>
       <c r="E42" t="s">
         <v>3333</v>
@@ -18384,16 +18435,16 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3514</v>
+        <v>3516</v>
       </c>
       <c r="B43" t="s">
         <v>3096</v>
       </c>
       <c r="C43" t="s">
-        <v>3433</v>
+        <v>3435</v>
       </c>
       <c r="D43" t="s">
-        <v>3515</v>
+        <v>3517</v>
       </c>
       <c r="E43" t="s">
         <v>3311</v>
@@ -18410,16 +18461,16 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3516</v>
+        <v>3518</v>
       </c>
       <c r="B44" t="s">
         <v>3096</v>
       </c>
       <c r="C44" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D44" t="s">
-        <v>3517</v>
+        <v>3519</v>
       </c>
       <c r="E44" t="s">
         <v>3334</v>
@@ -18436,16 +18487,16 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3518</v>
+        <v>3520</v>
       </c>
       <c r="B45" t="s">
         <v>3096</v>
       </c>
       <c r="C45" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D45" t="s">
-        <v>3519</v>
+        <v>3521</v>
       </c>
       <c r="E45" t="s">
         <v>3334</v>
@@ -18462,19 +18513,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3520</v>
+        <v>3522</v>
       </c>
       <c r="B46" t="s">
         <v>3094</v>
       </c>
       <c r="C46" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D46" t="s">
-        <v>3521</v>
+        <v>3523</v>
       </c>
       <c r="E46" t="s">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="F46" t="s">
         <v>3080</v>
@@ -18488,19 +18539,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3522</v>
+        <v>3524</v>
       </c>
       <c r="B47" t="s">
         <v>3094</v>
       </c>
       <c r="C47" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D47" t="s">
-        <v>3523</v>
+        <v>3525</v>
       </c>
       <c r="E47" t="s">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="F47" t="s">
         <v>3080</v>
@@ -18514,19 +18565,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3524</v>
+        <v>3526</v>
       </c>
       <c r="B48" t="s">
         <v>3092</v>
       </c>
       <c r="C48" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D48" t="s">
-        <v>3458</v>
+        <v>3460</v>
       </c>
       <c r="E48" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
       <c r="F48" t="s">
         <v>3080</v>
@@ -18540,19 +18591,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3525</v>
+        <v>3527</v>
       </c>
       <c r="B49" t="s">
         <v>3092</v>
       </c>
       <c r="C49" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D49" t="s">
-        <v>3526</v>
+        <v>3528</v>
       </c>
       <c r="E49" t="s">
-        <v>3409</v>
+        <v>3411</v>
       </c>
       <c r="F49" t="s">
         <v>3080</v>
@@ -18566,19 +18617,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3527</v>
+        <v>3529</v>
       </c>
       <c r="B50" t="s">
         <v>3092</v>
       </c>
       <c r="C50" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D50" t="s">
-        <v>3460</v>
+        <v>3462</v>
       </c>
       <c r="E50" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
       <c r="F50" t="s">
         <v>3080</v>
@@ -18592,19 +18643,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3528</v>
+        <v>3530</v>
       </c>
       <c r="B51" t="s">
         <v>3092</v>
       </c>
       <c r="C51" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D51" t="s">
-        <v>3483</v>
+        <v>3485</v>
       </c>
       <c r="E51" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
       <c r="F51" t="s">
         <v>3080</v>
@@ -18618,19 +18669,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3529</v>
+        <v>3531</v>
       </c>
       <c r="B52" t="s">
         <v>3094</v>
       </c>
       <c r="C52" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D52" t="s">
-        <v>3523</v>
+        <v>3525</v>
       </c>
       <c r="E52" t="s">
-        <v>3385</v>
+        <v>3387</v>
       </c>
       <c r="F52" t="s">
         <v>3080</v>
@@ -18644,19 +18695,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3530</v>
+        <v>3532</v>
       </c>
       <c r="B53" t="s">
         <v>3094</v>
       </c>
       <c r="C53" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D53" t="s">
-        <v>3519</v>
+        <v>3521</v>
       </c>
       <c r="E53" t="s">
-        <v>3385</v>
+        <v>3387</v>
       </c>
       <c r="F53" t="s">
         <v>3080</v>
@@ -18670,16 +18721,16 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3531</v>
+        <v>3533</v>
       </c>
       <c r="B54" t="s">
         <v>3096</v>
       </c>
       <c r="C54" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D54" t="s">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="E54" t="s">
         <v>3337</v>
@@ -18696,16 +18747,16 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3533</v>
+        <v>3535</v>
       </c>
       <c r="B55" t="s">
         <v>3096</v>
       </c>
       <c r="C55" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D55" t="s">
-        <v>3534</v>
+        <v>3536</v>
       </c>
       <c r="E55" t="s">
         <v>3337</v>
@@ -18722,19 +18773,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="B56" t="s">
         <v>3094</v>
       </c>
       <c r="C56" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D56" t="s">
-        <v>3519</v>
+        <v>3521</v>
       </c>
       <c r="E56" t="s">
-        <v>3387</v>
+        <v>3389</v>
       </c>
       <c r="F56" t="s">
         <v>3080</v>
@@ -18748,19 +18799,19 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="B57" t="s">
         <v>3094</v>
       </c>
       <c r="C57" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D57" t="s">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="E57" t="s">
-        <v>3387</v>
+        <v>3389</v>
       </c>
       <c r="F57" t="s">
         <v>3080</v>
@@ -18774,16 +18825,16 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3538</v>
+        <v>3540</v>
       </c>
       <c r="B58" t="s">
         <v>3096</v>
       </c>
       <c r="C58" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D58" t="s">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="E58" t="s">
         <v>3340</v>
@@ -18800,16 +18851,16 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="B59" t="s">
         <v>3096</v>
       </c>
       <c r="C59" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D59" t="s">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="E59" t="s">
         <v>3340</v>
@@ -18826,16 +18877,16 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3542</v>
+        <v>3544</v>
       </c>
       <c r="B60" t="s">
         <v>3096</v>
       </c>
       <c r="C60" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D60" t="s">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="E60" t="s">
         <v>3343</v>
@@ -18852,16 +18903,16 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3543</v>
+        <v>3545</v>
       </c>
       <c r="B61" t="s">
         <v>3096</v>
       </c>
       <c r="C61" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="D61" t="s">
-        <v>3544</v>
+        <v>3546</v>
       </c>
       <c r="E61" t="s">
         <v>3343</v>
@@ -18874,6 +18925,110 @@
       </c>
       <c r="H61" t="s">
         <v>3081</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>3547</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3449</v>
+      </c>
+      <c r="D62" t="s">
+        <v>3548</v>
+      </c>
+      <c r="E62" t="s">
+        <v>3549</v>
+      </c>
+      <c r="F62" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G62" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H62" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>3550</v>
+      </c>
+      <c r="B63" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3439</v>
+      </c>
+      <c r="D63" t="s">
+        <v>3551</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3552</v>
+      </c>
+      <c r="F63" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G63" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H63" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>3553</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3453</v>
+      </c>
+      <c r="D64" t="s">
+        <v>3498</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3554</v>
+      </c>
+      <c r="F64" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G64" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H64" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>3555</v>
+      </c>
+      <c r="B65" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3457</v>
+      </c>
+      <c r="D65" t="s">
+        <v>3501</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3349</v>
+      </c>
+      <c r="F65" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G65" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H65" t="s">
+        <v>3070</v>
       </c>
     </row>
   </sheetData>
@@ -39163,7 +39318,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -39171,7 +39326,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3545</v>
+        <v>3556</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>603</v>
@@ -39180,27 +39335,27 @@
         <v>604</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3428</v>
+        <v>3430</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>3546</v>
+        <v>3557</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3547</v>
+        <v>3558</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>3548</v>
+        <v>3559</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>3549</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3550</v>
+        <v>3561</v>
       </c>
       <c r="B2" t="s">
-        <v>3551</v>
+        <v>3562</v>
       </c>
       <c r="C2" t="s">
         <v>3066</v>
@@ -39212,24 +39367,24 @@
         <v>3070</v>
       </c>
       <c r="F2" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G2" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H2" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I2" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3556</v>
+        <v>3567</v>
       </c>
       <c r="B3" t="s">
-        <v>3557</v>
+        <v>3568</v>
       </c>
       <c r="C3" t="s">
         <v>3066</v>
@@ -39241,24 +39396,24 @@
         <v>3070</v>
       </c>
       <c r="F3" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G3" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H3" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I3" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3558</v>
+        <v>3569</v>
       </c>
       <c r="B4" t="s">
-        <v>3559</v>
+        <v>3570</v>
       </c>
       <c r="C4" t="s">
         <v>3066</v>
@@ -39270,24 +39425,24 @@
         <v>3070</v>
       </c>
       <c r="F4" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G4" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H4" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I4" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3560</v>
+        <v>3571</v>
       </c>
       <c r="B5" t="s">
-        <v>3561</v>
+        <v>3572</v>
       </c>
       <c r="C5" t="s">
         <v>3066</v>
@@ -39299,24 +39454,24 @@
         <v>3070</v>
       </c>
       <c r="F5" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G5" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H5" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I5" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3562</v>
+        <v>3573</v>
       </c>
       <c r="B6" t="s">
-        <v>3563</v>
+        <v>3574</v>
       </c>
       <c r="C6" t="s">
         <v>3066</v>
@@ -39328,24 +39483,24 @@
         <v>3070</v>
       </c>
       <c r="F6" t="s">
+        <v>3575</v>
+      </c>
+      <c r="G6" t="s">
         <v>3564</v>
       </c>
-      <c r="G6" t="s">
-        <v>3553</v>
-      </c>
       <c r="H6" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I6" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3565</v>
+        <v>3576</v>
       </c>
       <c r="B7" t="s">
-        <v>3566</v>
+        <v>3577</v>
       </c>
       <c r="C7" t="s">
         <v>3066</v>
@@ -39357,24 +39512,24 @@
         <v>3070</v>
       </c>
       <c r="F7" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G7" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H7" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I7" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3567</v>
+        <v>3578</v>
       </c>
       <c r="B8" t="s">
-        <v>3568</v>
+        <v>3579</v>
       </c>
       <c r="C8" t="s">
         <v>3066</v>
@@ -39386,24 +39541,24 @@
         <v>3070</v>
       </c>
       <c r="F8" t="s">
-        <v>3569</v>
+        <v>3580</v>
       </c>
       <c r="G8" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H8" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I8" t="s">
-        <v>3570</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3571</v>
+        <v>3582</v>
       </c>
       <c r="B9" t="s">
-        <v>3572</v>
+        <v>3583</v>
       </c>
       <c r="C9" t="s">
         <v>3066</v>
@@ -39415,24 +39570,24 @@
         <v>3070</v>
       </c>
       <c r="F9" t="s">
-        <v>3573</v>
+        <v>3584</v>
       </c>
       <c r="G9" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H9" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I9" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3574</v>
+        <v>3585</v>
       </c>
       <c r="B10" t="s">
-        <v>3575</v>
+        <v>3586</v>
       </c>
       <c r="C10" t="s">
         <v>3080</v>
@@ -39444,24 +39599,24 @@
         <v>3081</v>
       </c>
       <c r="F10" t="s">
-        <v>3576</v>
+        <v>3587</v>
       </c>
       <c r="G10" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H10" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I10" t="s">
-        <v>3579</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3580</v>
+        <v>3591</v>
       </c>
       <c r="B11" t="s">
-        <v>3581</v>
+        <v>3592</v>
       </c>
       <c r="C11" t="s">
         <v>3080</v>
@@ -39473,24 +39628,24 @@
         <v>3081</v>
       </c>
       <c r="F11" t="s">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="G11" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H11" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I11" t="s">
-        <v>3583</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3584</v>
+        <v>3595</v>
       </c>
       <c r="B12" t="s">
-        <v>3585</v>
+        <v>3596</v>
       </c>
       <c r="C12" t="s">
         <v>3080</v>
@@ -39502,24 +39657,24 @@
         <v>3081</v>
       </c>
       <c r="F12" t="s">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="G12" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H12" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I12" t="s">
-        <v>3586</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3587</v>
+        <v>3598</v>
       </c>
       <c r="B13" t="s">
-        <v>3588</v>
+        <v>3599</v>
       </c>
       <c r="C13" t="s">
         <v>3080</v>
@@ -39531,24 +39686,24 @@
         <v>3081</v>
       </c>
       <c r="F13" t="s">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="G13" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H13" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I13" t="s">
-        <v>3589</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3590</v>
+        <v>3601</v>
       </c>
       <c r="B14" t="s">
-        <v>3591</v>
+        <v>3602</v>
       </c>
       <c r="C14" t="s">
         <v>3080</v>
@@ -39560,24 +39715,24 @@
         <v>3081</v>
       </c>
       <c r="F14" t="s">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="G14" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H14" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I14" t="s">
-        <v>3592</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3593</v>
+        <v>3604</v>
       </c>
       <c r="B15" t="s">
-        <v>3594</v>
+        <v>3605</v>
       </c>
       <c r="C15" t="s">
         <v>3080</v>
@@ -39589,24 +39744,24 @@
         <v>3081</v>
       </c>
       <c r="F15" t="s">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="G15" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H15" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I15" t="s">
-        <v>3589</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3595</v>
+        <v>3606</v>
       </c>
       <c r="B16" t="s">
-        <v>3596</v>
+        <v>3607</v>
       </c>
       <c r="C16" t="s">
         <v>3080</v>
@@ -39618,24 +39773,24 @@
         <v>3081</v>
       </c>
       <c r="F16" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G16" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H16" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I16" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3597</v>
+        <v>3608</v>
       </c>
       <c r="B17" t="s">
-        <v>3598</v>
+        <v>3609</v>
       </c>
       <c r="C17" t="s">
         <v>3080</v>
@@ -39647,24 +39802,24 @@
         <v>3081</v>
       </c>
       <c r="F17" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G17" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H17" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I17" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3599</v>
+        <v>3610</v>
       </c>
       <c r="B18" t="s">
-        <v>3600</v>
+        <v>3611</v>
       </c>
       <c r="C18" t="s">
         <v>3080</v>
@@ -39676,24 +39831,24 @@
         <v>3081</v>
       </c>
       <c r="F18" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G18" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H18" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I18" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3601</v>
+        <v>3612</v>
       </c>
       <c r="B19" t="s">
-        <v>3602</v>
+        <v>3613</v>
       </c>
       <c r="C19" t="s">
         <v>3080</v>
@@ -39705,24 +39860,24 @@
         <v>3081</v>
       </c>
       <c r="F19" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G19" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H19" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I19" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3603</v>
+        <v>3614</v>
       </c>
       <c r="B20" t="s">
-        <v>3604</v>
+        <v>3615</v>
       </c>
       <c r="C20" t="s">
         <v>3080</v>
@@ -39734,24 +39889,24 @@
         <v>3081</v>
       </c>
       <c r="F20" t="s">
-        <v>3605</v>
+        <v>3616</v>
       </c>
       <c r="G20" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H20" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I20" t="s">
-        <v>3606</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3607</v>
+        <v>3618</v>
       </c>
       <c r="B21" t="s">
-        <v>3608</v>
+        <v>3619</v>
       </c>
       <c r="C21" t="s">
         <v>3080</v>
@@ -39763,24 +39918,24 @@
         <v>3081</v>
       </c>
       <c r="F21" t="s">
-        <v>3609</v>
+        <v>3620</v>
       </c>
       <c r="G21" t="s">
-        <v>3610</v>
+        <v>3621</v>
       </c>
       <c r="H21" t="s">
-        <v>3611</v>
+        <v>3622</v>
       </c>
       <c r="I21" t="s">
-        <v>3612</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3613</v>
+        <v>3624</v>
       </c>
       <c r="B22" t="s">
-        <v>3614</v>
+        <v>3625</v>
       </c>
       <c r="C22" t="s">
         <v>3080</v>
@@ -39792,24 +39947,24 @@
         <v>3081</v>
       </c>
       <c r="F22" t="s">
-        <v>3615</v>
+        <v>3626</v>
       </c>
       <c r="G22" t="s">
-        <v>3610</v>
+        <v>3621</v>
       </c>
       <c r="H22" t="s">
-        <v>3611</v>
+        <v>3622</v>
       </c>
       <c r="I22" t="s">
-        <v>3616</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3617</v>
+        <v>3628</v>
       </c>
       <c r="B23" t="s">
-        <v>3618</v>
+        <v>3629</v>
       </c>
       <c r="C23" t="s">
         <v>3080</v>
@@ -39821,24 +39976,24 @@
         <v>3081</v>
       </c>
       <c r="F23" t="s">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="G23" t="s">
-        <v>3577</v>
+        <v>3588</v>
       </c>
       <c r="H23" t="s">
-        <v>3578</v>
+        <v>3589</v>
       </c>
       <c r="I23" t="s">
-        <v>3592</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3619</v>
+        <v>3630</v>
       </c>
       <c r="B24" t="s">
-        <v>3620</v>
+        <v>3631</v>
       </c>
       <c r="C24" t="s">
         <v>3066</v>
@@ -39850,24 +40005,24 @@
         <v>3070</v>
       </c>
       <c r="F24" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G24" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H24" t="s">
-        <v>3622</v>
+        <v>3633</v>
       </c>
       <c r="I24" t="s">
-        <v>3623</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3624</v>
+        <v>3635</v>
       </c>
       <c r="B25" t="s">
-        <v>3625</v>
+        <v>3636</v>
       </c>
       <c r="C25" t="s">
         <v>3080</v>
@@ -39879,24 +40034,24 @@
         <v>3081</v>
       </c>
       <c r="F25" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G25" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H25" t="s">
-        <v>3622</v>
+        <v>3633</v>
       </c>
       <c r="I25" t="s">
-        <v>3627</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3628</v>
+        <v>3639</v>
       </c>
       <c r="B26" t="s">
-        <v>3629</v>
+        <v>3640</v>
       </c>
       <c r="C26" t="s">
         <v>3066</v>
@@ -39908,24 +40063,24 @@
         <v>3070</v>
       </c>
       <c r="F26" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G26" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H26" t="s">
-        <v>3630</v>
+        <v>3641</v>
       </c>
       <c r="I26" t="s">
-        <v>3631</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3632</v>
+        <v>3643</v>
       </c>
       <c r="B27" t="s">
-        <v>3633</v>
+        <v>3644</v>
       </c>
       <c r="C27" t="s">
         <v>3066</v>
@@ -39937,24 +40092,24 @@
         <v>3070</v>
       </c>
       <c r="F27" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G27" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H27" t="s">
-        <v>3630</v>
+        <v>3641</v>
       </c>
       <c r="I27" t="s">
-        <v>3634</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3635</v>
+        <v>3646</v>
       </c>
       <c r="B28" t="s">
-        <v>3636</v>
+        <v>3647</v>
       </c>
       <c r="C28" t="s">
         <v>3066</v>
@@ -39966,24 +40121,24 @@
         <v>3070</v>
       </c>
       <c r="F28" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G28" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H28" t="s">
-        <v>3637</v>
+        <v>3648</v>
       </c>
       <c r="I28" t="s">
-        <v>3623</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3638</v>
+        <v>3649</v>
       </c>
       <c r="B29" t="s">
-        <v>3639</v>
+        <v>3650</v>
       </c>
       <c r="C29" t="s">
         <v>3080</v>
@@ -39995,24 +40150,24 @@
         <v>3081</v>
       </c>
       <c r="F29" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G29" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H29" t="s">
-        <v>3637</v>
+        <v>3648</v>
       </c>
       <c r="I29" t="s">
-        <v>3627</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3640</v>
+        <v>3651</v>
       </c>
       <c r="B30" t="s">
-        <v>3641</v>
+        <v>3652</v>
       </c>
       <c r="C30" t="s">
         <v>3066</v>
@@ -40024,24 +40179,24 @@
         <v>3070</v>
       </c>
       <c r="F30" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G30" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H30" t="s">
-        <v>3642</v>
+        <v>3653</v>
       </c>
       <c r="I30" t="s">
-        <v>3643</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3644</v>
+        <v>3655</v>
       </c>
       <c r="B31" t="s">
-        <v>3645</v>
+        <v>3656</v>
       </c>
       <c r="C31" t="s">
         <v>3066</v>
@@ -40053,24 +40208,24 @@
         <v>3070</v>
       </c>
       <c r="F31" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G31" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H31" t="s">
-        <v>3642</v>
+        <v>3653</v>
       </c>
       <c r="I31" t="s">
-        <v>3646</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3647</v>
+        <v>3658</v>
       </c>
       <c r="B32" t="s">
-        <v>3648</v>
+        <v>3659</v>
       </c>
       <c r="C32" t="s">
         <v>3066</v>
@@ -40082,24 +40237,24 @@
         <v>3070</v>
       </c>
       <c r="F32" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G32" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H32" t="s">
-        <v>3649</v>
+        <v>3660</v>
       </c>
       <c r="I32" t="s">
-        <v>3623</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3650</v>
+        <v>3661</v>
       </c>
       <c r="B33" t="s">
-        <v>3651</v>
+        <v>3662</v>
       </c>
       <c r="C33" t="s">
         <v>3066</v>
@@ -40111,24 +40266,24 @@
         <v>3070</v>
       </c>
       <c r="F33" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G33" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H33" t="s">
-        <v>3649</v>
+        <v>3660</v>
       </c>
       <c r="I33" t="s">
-        <v>3627</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3652</v>
+        <v>3663</v>
       </c>
       <c r="B34" t="s">
-        <v>3653</v>
+        <v>3664</v>
       </c>
       <c r="C34" t="s">
         <v>3066</v>
@@ -40140,24 +40295,24 @@
         <v>3070</v>
       </c>
       <c r="F34" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G34" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H34" t="s">
-        <v>3654</v>
+        <v>3665</v>
       </c>
       <c r="I34" t="s">
-        <v>3655</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3656</v>
+        <v>3667</v>
       </c>
       <c r="B35" t="s">
-        <v>3657</v>
+        <v>3668</v>
       </c>
       <c r="C35" t="s">
         <v>3066</v>
@@ -40169,24 +40324,24 @@
         <v>3070</v>
       </c>
       <c r="F35" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G35" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H35" t="s">
-        <v>3654</v>
+        <v>3665</v>
       </c>
       <c r="I35" t="s">
-        <v>3658</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3659</v>
+        <v>3670</v>
       </c>
       <c r="B36" t="s">
-        <v>3660</v>
+        <v>3671</v>
       </c>
       <c r="C36" t="s">
         <v>3066</v>
@@ -40198,24 +40353,24 @@
         <v>3070</v>
       </c>
       <c r="F36" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G36" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H36" t="s">
-        <v>3661</v>
+        <v>3672</v>
       </c>
       <c r="I36" t="s">
-        <v>3655</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3662</v>
+        <v>3673</v>
       </c>
       <c r="B37" t="s">
-        <v>3663</v>
+        <v>3674</v>
       </c>
       <c r="C37" t="s">
         <v>3066</v>
@@ -40227,24 +40382,24 @@
         <v>3070</v>
       </c>
       <c r="F37" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G37" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H37" t="s">
-        <v>3661</v>
+        <v>3672</v>
       </c>
       <c r="I37" t="s">
-        <v>3658</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3664</v>
+        <v>3675</v>
       </c>
       <c r="B38" t="s">
-        <v>3665</v>
+        <v>3676</v>
       </c>
       <c r="C38" t="s">
         <v>3066</v>
@@ -40256,24 +40411,24 @@
         <v>3070</v>
       </c>
       <c r="F38" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G38" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H38" t="s">
-        <v>3666</v>
+        <v>3677</v>
       </c>
       <c r="I38" t="s">
-        <v>3623</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3667</v>
+        <v>3678</v>
       </c>
       <c r="B39" t="s">
-        <v>3668</v>
+        <v>3679</v>
       </c>
       <c r="C39" t="s">
         <v>3066</v>
@@ -40285,24 +40440,24 @@
         <v>3070</v>
       </c>
       <c r="F39" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G39" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H39" t="s">
-        <v>3666</v>
+        <v>3677</v>
       </c>
       <c r="I39" t="s">
-        <v>3627</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3669</v>
+        <v>3680</v>
       </c>
       <c r="B40" t="s">
-        <v>3670</v>
+        <v>3681</v>
       </c>
       <c r="C40" t="s">
         <v>3066</v>
@@ -40314,24 +40469,24 @@
         <v>3070</v>
       </c>
       <c r="F40" t="s">
-        <v>3621</v>
+        <v>3632</v>
       </c>
       <c r="G40" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H40" t="s">
-        <v>3671</v>
+        <v>3682</v>
       </c>
       <c r="I40" t="s">
-        <v>3672</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3673</v>
+        <v>3684</v>
       </c>
       <c r="B41" t="s">
-        <v>3674</v>
+        <v>3685</v>
       </c>
       <c r="C41" t="s">
         <v>3066</v>
@@ -40343,21 +40498,21 @@
         <v>3070</v>
       </c>
       <c r="F41" t="s">
-        <v>3626</v>
+        <v>3637</v>
       </c>
       <c r="G41" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H41" t="s">
-        <v>3671</v>
+        <v>3682</v>
       </c>
       <c r="I41" t="s">
-        <v>3675</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3676</v>
+        <v>3687</v>
       </c>
       <c r="B42" t="s">
         <v>3295</v>
@@ -40372,24 +40527,24 @@
         <v>3081</v>
       </c>
       <c r="F42" t="s">
-        <v>3677</v>
+        <v>3688</v>
       </c>
       <c r="G42" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H42" t="s">
         <v>3096</v>
       </c>
       <c r="I42" t="s">
-        <v>3678</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3679</v>
+        <v>3690</v>
       </c>
       <c r="B43" t="s">
-        <v>3680</v>
+        <v>3691</v>
       </c>
       <c r="C43" t="s">
         <v>3080</v>
@@ -40401,24 +40556,24 @@
         <v>3081</v>
       </c>
       <c r="F43" t="s">
-        <v>3569</v>
+        <v>3580</v>
       </c>
       <c r="G43" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H43" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I43" t="s">
-        <v>3570</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3681</v>
+        <v>3692</v>
       </c>
       <c r="B44" t="s">
-        <v>3435</v>
+        <v>3437</v>
       </c>
       <c r="C44" t="s">
         <v>3066</v>
@@ -40430,21 +40585,21 @@
         <v>3070</v>
       </c>
       <c r="F44" t="s">
-        <v>3682</v>
+        <v>3693</v>
       </c>
       <c r="G44" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H44" t="s">
         <v>3096</v>
       </c>
       <c r="I44" t="s">
-        <v>3683</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3684</v>
+        <v>3695</v>
       </c>
       <c r="B45" t="s">
         <v>3296</v>
@@ -40459,24 +40614,24 @@
         <v>3070</v>
       </c>
       <c r="F45" t="s">
-        <v>3685</v>
+        <v>3696</v>
       </c>
       <c r="G45" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H45" t="s">
         <v>3096</v>
       </c>
       <c r="I45" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3686</v>
+        <v>3697</v>
       </c>
       <c r="B46" t="s">
-        <v>3445</v>
+        <v>3447</v>
       </c>
       <c r="C46" t="s">
         <v>3066</v>
@@ -40488,24 +40643,24 @@
         <v>3070</v>
       </c>
       <c r="F46" t="s">
-        <v>3605</v>
+        <v>3616</v>
       </c>
       <c r="G46" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H46" t="s">
         <v>3096</v>
       </c>
       <c r="I46" t="s">
-        <v>3606</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3687</v>
+        <v>3698</v>
       </c>
       <c r="B47" t="s">
-        <v>3688</v>
+        <v>3699</v>
       </c>
       <c r="C47" t="s">
         <v>3066</v>
@@ -40517,24 +40672,24 @@
         <v>3070</v>
       </c>
       <c r="F47" t="s">
-        <v>3689</v>
+        <v>3700</v>
       </c>
       <c r="G47" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H47" t="s">
         <v>3096</v>
       </c>
       <c r="I47" t="s">
-        <v>3690</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3691</v>
+        <v>3702</v>
       </c>
       <c r="B48" t="s">
-        <v>3692</v>
+        <v>3703</v>
       </c>
       <c r="C48" t="s">
         <v>3066</v>
@@ -40546,24 +40701,24 @@
         <v>3070</v>
       </c>
       <c r="F48" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G48" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H48" t="s">
         <v>3096</v>
       </c>
       <c r="I48" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3693</v>
+        <v>3704</v>
       </c>
       <c r="B49" t="s">
-        <v>3694</v>
+        <v>3705</v>
       </c>
       <c r="C49" t="s">
         <v>3080</v>
@@ -40575,21 +40730,21 @@
         <v>3081</v>
       </c>
       <c r="F49" t="s">
-        <v>3569</v>
+        <v>3580</v>
       </c>
       <c r="G49" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H49" t="s">
         <v>3096</v>
       </c>
       <c r="I49" t="s">
-        <v>3570</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3695</v>
+        <v>3706</v>
       </c>
       <c r="B50" t="s">
         <v>3320</v>
@@ -40604,21 +40759,21 @@
         <v>3081</v>
       </c>
       <c r="F50" t="s">
-        <v>3573</v>
+        <v>3584</v>
       </c>
       <c r="G50" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H50" t="s">
         <v>3096</v>
       </c>
       <c r="I50" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3696</v>
+        <v>3707</v>
       </c>
       <c r="B51" t="s">
         <v>3321</v>
@@ -40633,21 +40788,21 @@
         <v>3081</v>
       </c>
       <c r="F51" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G51" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H51" t="s">
         <v>3096</v>
       </c>
       <c r="I51" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3697</v>
+        <v>3708</v>
       </c>
       <c r="B52" t="s">
         <v>3300</v>
@@ -40662,24 +40817,24 @@
         <v>3081</v>
       </c>
       <c r="F52" t="s">
-        <v>3677</v>
+        <v>3688</v>
       </c>
       <c r="G52" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H52" t="s">
         <v>3094</v>
       </c>
       <c r="I52" t="s">
-        <v>3698</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3699</v>
+        <v>3710</v>
       </c>
       <c r="B53" t="s">
-        <v>3700</v>
+        <v>3711</v>
       </c>
       <c r="C53" t="s">
         <v>3080</v>
@@ -40691,24 +40846,24 @@
         <v>3081</v>
       </c>
       <c r="F53" t="s">
-        <v>3573</v>
+        <v>3584</v>
       </c>
       <c r="G53" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H53" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I53" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3701</v>
+        <v>3712</v>
       </c>
       <c r="B54" t="s">
-        <v>3702</v>
+        <v>3713</v>
       </c>
       <c r="C54" t="s">
         <v>3080</v>
@@ -40720,24 +40875,24 @@
         <v>3081</v>
       </c>
       <c r="F54" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G54" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H54" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I54" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3703</v>
+        <v>3714</v>
       </c>
       <c r="B55" t="s">
-        <v>3704</v>
+        <v>3715</v>
       </c>
       <c r="C55" t="s">
         <v>3080</v>
@@ -40749,21 +40904,21 @@
         <v>3081</v>
       </c>
       <c r="F55" t="s">
-        <v>3705</v>
+        <v>3716</v>
       </c>
       <c r="G55" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H55" t="s">
-        <v>3554</v>
+        <v>3565</v>
       </c>
       <c r="I55" t="s">
-        <v>3706</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3707</v>
+        <v>3718</v>
       </c>
       <c r="B56" t="s">
         <v>3307</v>
@@ -40778,21 +40933,21 @@
         <v>3081</v>
       </c>
       <c r="F56" t="s">
-        <v>3682</v>
+        <v>3693</v>
       </c>
       <c r="G56" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H56" t="s">
         <v>3094</v>
       </c>
       <c r="I56" t="s">
-        <v>3708</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3709</v>
+        <v>3720</v>
       </c>
       <c r="B57" t="s">
         <v>3301</v>
@@ -40807,24 +40962,24 @@
         <v>3081</v>
       </c>
       <c r="F57" t="s">
-        <v>3685</v>
+        <v>3696</v>
       </c>
       <c r="G57" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H57" t="s">
         <v>3094</v>
       </c>
       <c r="I57" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3711</v>
+        <v>3722</v>
       </c>
       <c r="B58" t="s">
-        <v>3362</v>
+        <v>3364</v>
       </c>
       <c r="C58" t="s">
         <v>3080</v>
@@ -40836,24 +40991,24 @@
         <v>3081</v>
       </c>
       <c r="F58" t="s">
+        <v>3575</v>
+      </c>
+      <c r="G58" t="s">
         <v>3564</v>
-      </c>
-      <c r="G58" t="s">
-        <v>3553</v>
       </c>
       <c r="H58" t="s">
         <v>3094</v>
       </c>
       <c r="I58" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3712</v>
+        <v>3723</v>
       </c>
       <c r="B59" t="s">
-        <v>3713</v>
+        <v>3724</v>
       </c>
       <c r="C59" t="s">
         <v>3080</v>
@@ -40865,24 +41020,24 @@
         <v>3081</v>
       </c>
       <c r="F59" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G59" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H59" t="s">
         <v>3094</v>
       </c>
       <c r="I59" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3714</v>
+        <v>3725</v>
       </c>
       <c r="B60" t="s">
-        <v>3715</v>
+        <v>3726</v>
       </c>
       <c r="C60" t="s">
         <v>3080</v>
@@ -40894,24 +41049,24 @@
         <v>3081</v>
       </c>
       <c r="F60" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G60" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H60" t="s">
         <v>3094</v>
       </c>
       <c r="I60" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3716</v>
+        <v>3727</v>
       </c>
       <c r="B61" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="C61" t="s">
         <v>3080</v>
@@ -40923,24 +41078,24 @@
         <v>3081</v>
       </c>
       <c r="F61" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G61" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H61" t="s">
         <v>3094</v>
       </c>
       <c r="I61" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3717</v>
+        <v>3728</v>
       </c>
       <c r="B62" t="s">
-        <v>3367</v>
+        <v>3369</v>
       </c>
       <c r="C62" t="s">
         <v>3080</v>
@@ -40952,21 +41107,21 @@
         <v>3081</v>
       </c>
       <c r="F62" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G62" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H62" t="s">
         <v>3094</v>
       </c>
       <c r="I62" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3718</v>
+        <v>3729</v>
       </c>
       <c r="B63" t="s">
         <v>3324</v>
@@ -40981,24 +41136,24 @@
         <v>3081</v>
       </c>
       <c r="F63" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G63" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H63" t="s">
         <v>3096</v>
       </c>
       <c r="I63" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3719</v>
+        <v>3730</v>
       </c>
       <c r="B64" t="s">
-        <v>3487</v>
+        <v>3489</v>
       </c>
       <c r="C64" t="s">
         <v>3080</v>
@@ -41010,21 +41165,21 @@
         <v>3081</v>
       </c>
       <c r="F64" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G64" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H64" t="s">
         <v>3094</v>
       </c>
       <c r="I64" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3720</v>
+        <v>3731</v>
       </c>
       <c r="B65" t="s">
         <v>3302</v>
@@ -41039,21 +41194,21 @@
         <v>3081</v>
       </c>
       <c r="F65" t="s">
-        <v>3677</v>
+        <v>3688</v>
       </c>
       <c r="G65" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H65" t="s">
         <v>3092</v>
       </c>
       <c r="I65" t="s">
-        <v>3678</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3721</v>
+        <v>3732</v>
       </c>
       <c r="B66" t="s">
         <v>3309</v>
@@ -41068,21 +41223,21 @@
         <v>3070</v>
       </c>
       <c r="F66" t="s">
-        <v>3682</v>
+        <v>3693</v>
       </c>
       <c r="G66" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H66" t="s">
         <v>3092</v>
       </c>
       <c r="I66" t="s">
-        <v>3683</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3722</v>
+        <v>3733</v>
       </c>
       <c r="B67" t="s">
         <v>3303</v>
@@ -41097,24 +41252,24 @@
         <v>3070</v>
       </c>
       <c r="F67" t="s">
-        <v>3685</v>
+        <v>3696</v>
       </c>
       <c r="G67" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H67" t="s">
         <v>3092</v>
       </c>
       <c r="I67" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3723</v>
+        <v>3734</v>
       </c>
       <c r="B68" t="s">
-        <v>3411</v>
+        <v>3413</v>
       </c>
       <c r="C68" t="s">
         <v>3066</v>
@@ -41126,24 +41281,24 @@
         <v>3070</v>
       </c>
       <c r="F68" t="s">
+        <v>3575</v>
+      </c>
+      <c r="G68" t="s">
         <v>3564</v>
-      </c>
-      <c r="G68" t="s">
-        <v>3553</v>
       </c>
       <c r="H68" t="s">
         <v>3092</v>
       </c>
       <c r="I68" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3724</v>
+        <v>3735</v>
       </c>
       <c r="B69" t="s">
-        <v>3497</v>
+        <v>3499</v>
       </c>
       <c r="C69" t="s">
         <v>3066</v>
@@ -41155,24 +41310,24 @@
         <v>3070</v>
       </c>
       <c r="F69" t="s">
-        <v>3569</v>
+        <v>3580</v>
       </c>
       <c r="G69" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H69" t="s">
         <v>3094</v>
       </c>
       <c r="I69" t="s">
-        <v>3725</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3726</v>
+        <v>3737</v>
       </c>
       <c r="B70" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
       <c r="C70" t="s">
         <v>3066</v>
@@ -41184,24 +41339,24 @@
         <v>3070</v>
       </c>
       <c r="F70" t="s">
-        <v>3573</v>
+        <v>3584</v>
       </c>
       <c r="G70" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H70" t="s">
         <v>3094</v>
       </c>
       <c r="I70" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3727</v>
+        <v>3738</v>
       </c>
       <c r="B71" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="C71" t="s">
         <v>3066</v>
@@ -41213,24 +41368,24 @@
         <v>3070</v>
       </c>
       <c r="F71" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G71" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H71" t="s">
         <v>3094</v>
       </c>
       <c r="I71" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3728</v>
+        <v>3739</v>
       </c>
       <c r="B72" t="s">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="C72" t="s">
         <v>3066</v>
@@ -41242,21 +41397,21 @@
         <v>3070</v>
       </c>
       <c r="F72" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G72" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H72" t="s">
         <v>3094</v>
       </c>
       <c r="I72" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3729</v>
+        <v>3740</v>
       </c>
       <c r="B73" t="s">
         <v>3327</v>
@@ -41271,21 +41426,21 @@
         <v>3070</v>
       </c>
       <c r="F73" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G73" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H73" t="s">
         <v>3096</v>
       </c>
       <c r="I73" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3730</v>
+        <v>3741</v>
       </c>
       <c r="B74" t="s">
         <v>3333</v>
@@ -41300,21 +41455,21 @@
         <v>3070</v>
       </c>
       <c r="F74" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G74" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H74" t="s">
         <v>3096</v>
       </c>
       <c r="I74" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3731</v>
+        <v>3742</v>
       </c>
       <c r="B75" t="s">
         <v>3311</v>
@@ -41329,21 +41484,21 @@
         <v>3070</v>
       </c>
       <c r="F75" t="s">
-        <v>3682</v>
+        <v>3693</v>
       </c>
       <c r="G75" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H75" t="s">
         <v>3096</v>
       </c>
       <c r="I75" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3732</v>
+        <v>3743</v>
       </c>
       <c r="B76" t="s">
         <v>3334</v>
@@ -41358,24 +41513,24 @@
         <v>3081</v>
       </c>
       <c r="F76" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G76" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H76" t="s">
         <v>3096</v>
       </c>
       <c r="I76" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3733</v>
+        <v>3744</v>
       </c>
       <c r="B77" t="s">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="C77" t="s">
         <v>3080</v>
@@ -41387,24 +41542,24 @@
         <v>3081</v>
       </c>
       <c r="F77" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G77" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H77" t="s">
         <v>3094</v>
       </c>
       <c r="I77" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3734</v>
+        <v>3745</v>
       </c>
       <c r="B78" t="s">
-        <v>3735</v>
+        <v>3746</v>
       </c>
       <c r="C78" t="s">
         <v>3080</v>
@@ -41416,24 +41571,24 @@
         <v>3081</v>
       </c>
       <c r="F78" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G78" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H78" t="s">
         <v>3092</v>
       </c>
       <c r="I78" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3736</v>
+        <v>3747</v>
       </c>
       <c r="B79" t="s">
-        <v>3409</v>
+        <v>3411</v>
       </c>
       <c r="C79" t="s">
         <v>3080</v>
@@ -41445,24 +41600,24 @@
         <v>3081</v>
       </c>
       <c r="F79" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G79" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H79" t="s">
         <v>3092</v>
       </c>
       <c r="I79" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3737</v>
+        <v>3748</v>
       </c>
       <c r="B80" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
       <c r="C80" t="s">
         <v>3080</v>
@@ -41474,24 +41629,24 @@
         <v>3081</v>
       </c>
       <c r="F80" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G80" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H80" t="s">
         <v>3092</v>
       </c>
       <c r="I80" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3738</v>
+        <v>3749</v>
       </c>
       <c r="B81" t="s">
-        <v>3385</v>
+        <v>3387</v>
       </c>
       <c r="C81" t="s">
         <v>3080</v>
@@ -41503,24 +41658,24 @@
         <v>3081</v>
       </c>
       <c r="F81" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G81" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H81" t="s">
         <v>3094</v>
       </c>
       <c r="I81" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3739</v>
+        <v>3750</v>
       </c>
       <c r="B82" t="s">
-        <v>3740</v>
+        <v>3751</v>
       </c>
       <c r="C82" t="s">
         <v>3066</v>
@@ -41532,24 +41687,24 @@
         <v>3070</v>
       </c>
       <c r="F82" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G82" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H82" t="s">
         <v>3096</v>
       </c>
       <c r="I82" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3741</v>
+        <v>3752</v>
       </c>
       <c r="B83" t="s">
-        <v>3387</v>
+        <v>3389</v>
       </c>
       <c r="C83" t="s">
         <v>3080</v>
@@ -41561,21 +41716,21 @@
         <v>3081</v>
       </c>
       <c r="F83" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G83" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H83" t="s">
         <v>3094</v>
       </c>
       <c r="I83" t="s">
-        <v>3710</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3742</v>
+        <v>3753</v>
       </c>
       <c r="B84" t="s">
         <v>3340</v>
@@ -41590,21 +41745,21 @@
         <v>3081</v>
       </c>
       <c r="F84" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G84" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H84" t="s">
         <v>3096</v>
       </c>
       <c r="I84" t="s">
-        <v>3555</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3743</v>
+        <v>3754</v>
       </c>
       <c r="B85" t="s">
         <v>3343</v>
@@ -41619,16 +41774,132 @@
         <v>3081</v>
       </c>
       <c r="F85" t="s">
-        <v>3552</v>
+        <v>3563</v>
       </c>
       <c r="G85" t="s">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="H85" t="s">
         <v>3096</v>
       </c>
       <c r="I85" t="s">
-        <v>3555</v>
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>3755</v>
+      </c>
+      <c r="B86" t="s">
+        <v>3756</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D86" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3070</v>
+      </c>
+      <c r="F86" t="s">
+        <v>3563</v>
+      </c>
+      <c r="G86" t="s">
+        <v>3564</v>
+      </c>
+      <c r="H86" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I86" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>3757</v>
+      </c>
+      <c r="B87" t="s">
+        <v>3552</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D87" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E87" t="s">
+        <v>3070</v>
+      </c>
+      <c r="F87" t="s">
+        <v>3575</v>
+      </c>
+      <c r="G87" t="s">
+        <v>3564</v>
+      </c>
+      <c r="H87" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I87" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>3758</v>
+      </c>
+      <c r="B88" t="s">
+        <v>3759</v>
+      </c>
+      <c r="C88" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D88" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E88" t="s">
+        <v>3070</v>
+      </c>
+      <c r="F88" t="s">
+        <v>3580</v>
+      </c>
+      <c r="G88" t="s">
+        <v>3564</v>
+      </c>
+      <c r="H88" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I88" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>3760</v>
+      </c>
+      <c r="B89" t="s">
+        <v>3349</v>
+      </c>
+      <c r="C89" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D89" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E89" t="s">
+        <v>3070</v>
+      </c>
+      <c r="F89" t="s">
+        <v>3584</v>
+      </c>
+      <c r="G89" t="s">
+        <v>3564</v>
+      </c>
+      <c r="H89" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I89" t="s">
+        <v>3566</v>
       </c>
     </row>
   </sheetData>

--- a/data/workshop.xlsx
+++ b/data/workshop.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10220" uniqueCount="4043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10254" uniqueCount="4050">
   <si>
     <t>id</t>
   </si>
@@ -10139,7 +10139,7 @@
     <t>Test Bench &amp; Completed: Test</t>
   </si>
   <si>
-    <t>2026-08-13T13:20:04.780Z</t>
+    <t>2026-08-13T14:42:27.873Z</t>
   </si>
   <si>
     <t>3edd89d2-41a4-4856-976b-cbc716dc3788</t>
@@ -11333,6 +11333,18 @@
     <t>Assemble: Clutch 3 · oleh Administrator (superuser)</t>
   </si>
   <si>
+    <t>c33c5a61-dfc8-44fd-bbfa-3f7815c44eaa</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:42:14.311Z</t>
+  </si>
+  <si>
+    <t>11229d53-221d-4549-be09-8f9aeadcbc82</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:42:28.030Z</t>
+  </si>
+  <si>
     <t>at</t>
   </si>
   <si>
@@ -12156,6 +12168,15 @@
   </si>
   <si>
     <t>f1a199c0-1f7d-4a8d-85ac-b2683d15d5f7</t>
+  </si>
+  <si>
+    <t>a8c5d168-af13-4636-8ee0-da06e7560cdb</t>
+  </si>
+  <si>
+    <t>87bc2cc3-e761-41f1-8af9-d7140a87c309</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:42:28.031Z</t>
   </si>
 </sst>
 </file>
@@ -16438,7 +16459,7 @@
         <v>19</v>
       </c>
       <c r="M2">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="N2">
         <v>5340</v>
@@ -17185,7 +17206,7 @@
         <v>19</v>
       </c>
       <c r="H14">
-        <v>4740</v>
+        <v>9667</v>
       </c>
       <c r="I14">
         <v>300</v>
@@ -19142,7 +19163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22652,6 +22673,58 @@
         <v>3069</v>
       </c>
       <c r="H135" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B136" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C136" t="s">
+        <v>3525</v>
+      </c>
+      <c r="D136" t="s">
+        <v>3570</v>
+      </c>
+      <c r="E136" t="s">
+        <v>3769</v>
+      </c>
+      <c r="F136" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G136" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H136" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>3770</v>
+      </c>
+      <c r="B137" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C137" t="s">
+        <v>3529</v>
+      </c>
+      <c r="D137" t="s">
+        <v>3573</v>
+      </c>
+      <c r="E137" t="s">
+        <v>3771</v>
+      </c>
+      <c r="F137" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G137" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H137" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -42942,7 +43015,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -42950,7 +43023,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3768</v>
+        <v>3772</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>603</v>
@@ -42962,24 +43035,24 @@
         <v>3502</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>3769</v>
+        <v>3773</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3770</v>
+        <v>3774</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>3771</v>
+        <v>3775</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>3772</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3773</v>
+        <v>3777</v>
       </c>
       <c r="B2" t="s">
-        <v>3774</v>
+        <v>3778</v>
       </c>
       <c r="C2" t="s">
         <v>3066</v>
@@ -42991,24 +43064,24 @@
         <v>3070</v>
       </c>
       <c r="F2" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G2" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H2" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I2" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3779</v>
+        <v>3783</v>
       </c>
       <c r="B3" t="s">
-        <v>3780</v>
+        <v>3784</v>
       </c>
       <c r="C3" t="s">
         <v>3066</v>
@@ -43020,24 +43093,24 @@
         <v>3070</v>
       </c>
       <c r="F3" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G3" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H3" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I3" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3781</v>
+        <v>3785</v>
       </c>
       <c r="B4" t="s">
-        <v>3782</v>
+        <v>3786</v>
       </c>
       <c r="C4" t="s">
         <v>3066</v>
@@ -43049,24 +43122,24 @@
         <v>3070</v>
       </c>
       <c r="F4" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G4" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H4" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I4" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3783</v>
+        <v>3787</v>
       </c>
       <c r="B5" t="s">
-        <v>3784</v>
+        <v>3788</v>
       </c>
       <c r="C5" t="s">
         <v>3066</v>
@@ -43078,24 +43151,24 @@
         <v>3070</v>
       </c>
       <c r="F5" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G5" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H5" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I5" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3785</v>
+        <v>3789</v>
       </c>
       <c r="B6" t="s">
-        <v>3786</v>
+        <v>3790</v>
       </c>
       <c r="C6" t="s">
         <v>3066</v>
@@ -43107,24 +43180,24 @@
         <v>3070</v>
       </c>
       <c r="F6" t="s">
-        <v>3787</v>
+        <v>3791</v>
       </c>
       <c r="G6" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H6" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I6" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3788</v>
+        <v>3792</v>
       </c>
       <c r="B7" t="s">
-        <v>3789</v>
+        <v>3793</v>
       </c>
       <c r="C7" t="s">
         <v>3066</v>
@@ -43136,24 +43209,24 @@
         <v>3070</v>
       </c>
       <c r="F7" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G7" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H7" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I7" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3790</v>
+        <v>3794</v>
       </c>
       <c r="B8" t="s">
-        <v>3791</v>
+        <v>3795</v>
       </c>
       <c r="C8" t="s">
         <v>3066</v>
@@ -43165,24 +43238,24 @@
         <v>3070</v>
       </c>
       <c r="F8" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G8" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H8" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I8" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3794</v>
+        <v>3798</v>
       </c>
       <c r="B9" t="s">
-        <v>3795</v>
+        <v>3799</v>
       </c>
       <c r="C9" t="s">
         <v>3066</v>
@@ -43194,24 +43267,24 @@
         <v>3070</v>
       </c>
       <c r="F9" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G9" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H9" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I9" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3797</v>
+        <v>3801</v>
       </c>
       <c r="B10" t="s">
-        <v>3798</v>
+        <v>3802</v>
       </c>
       <c r="C10" t="s">
         <v>3080</v>
@@ -43223,24 +43296,24 @@
         <v>3081</v>
       </c>
       <c r="F10" t="s">
-        <v>3799</v>
+        <v>3803</v>
       </c>
       <c r="G10" t="s">
-        <v>3800</v>
+        <v>3804</v>
       </c>
       <c r="H10" t="s">
-        <v>3801</v>
+        <v>3805</v>
       </c>
       <c r="I10" t="s">
-        <v>3802</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3803</v>
+        <v>3807</v>
       </c>
       <c r="B11" t="s">
-        <v>3804</v>
+        <v>3808</v>
       </c>
       <c r="C11" t="s">
         <v>3080</v>
@@ -43252,24 +43325,24 @@
         <v>3081</v>
       </c>
       <c r="F11" t="s">
+        <v>3809</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3804</v>
+      </c>
+      <c r="H11" t="s">
         <v>3805</v>
       </c>
-      <c r="G11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="H11" t="s">
-        <v>3801</v>
-      </c>
       <c r="I11" t="s">
-        <v>3806</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3807</v>
+        <v>3811</v>
       </c>
       <c r="B12" t="s">
-        <v>3808</v>
+        <v>3812</v>
       </c>
       <c r="C12" t="s">
         <v>3080</v>
@@ -43281,24 +43354,24 @@
         <v>3081</v>
       </c>
       <c r="F12" t="s">
+        <v>3809</v>
+      </c>
+      <c r="G12" t="s">
+        <v>3804</v>
+      </c>
+      <c r="H12" t="s">
         <v>3805</v>
       </c>
-      <c r="G12" t="s">
-        <v>3800</v>
-      </c>
-      <c r="H12" t="s">
-        <v>3801</v>
-      </c>
       <c r="I12" t="s">
-        <v>3809</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3810</v>
+        <v>3814</v>
       </c>
       <c r="B13" t="s">
-        <v>3811</v>
+        <v>3815</v>
       </c>
       <c r="C13" t="s">
         <v>3080</v>
@@ -43310,24 +43383,24 @@
         <v>3081</v>
       </c>
       <c r="F13" t="s">
+        <v>3809</v>
+      </c>
+      <c r="G13" t="s">
+        <v>3804</v>
+      </c>
+      <c r="H13" t="s">
         <v>3805</v>
       </c>
-      <c r="G13" t="s">
-        <v>3800</v>
-      </c>
-      <c r="H13" t="s">
-        <v>3801</v>
-      </c>
       <c r="I13" t="s">
-        <v>3812</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3813</v>
+        <v>3817</v>
       </c>
       <c r="B14" t="s">
-        <v>3814</v>
+        <v>3818</v>
       </c>
       <c r="C14" t="s">
         <v>3080</v>
@@ -43339,24 +43412,24 @@
         <v>3081</v>
       </c>
       <c r="F14" t="s">
+        <v>3809</v>
+      </c>
+      <c r="G14" t="s">
+        <v>3804</v>
+      </c>
+      <c r="H14" t="s">
         <v>3805</v>
       </c>
-      <c r="G14" t="s">
-        <v>3800</v>
-      </c>
-      <c r="H14" t="s">
-        <v>3801</v>
-      </c>
       <c r="I14" t="s">
-        <v>3815</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3816</v>
+        <v>3820</v>
       </c>
       <c r="B15" t="s">
-        <v>3817</v>
+        <v>3821</v>
       </c>
       <c r="C15" t="s">
         <v>3080</v>
@@ -43368,24 +43441,24 @@
         <v>3081</v>
       </c>
       <c r="F15" t="s">
+        <v>3809</v>
+      </c>
+      <c r="G15" t="s">
+        <v>3804</v>
+      </c>
+      <c r="H15" t="s">
         <v>3805</v>
       </c>
-      <c r="G15" t="s">
-        <v>3800</v>
-      </c>
-      <c r="H15" t="s">
-        <v>3801</v>
-      </c>
       <c r="I15" t="s">
-        <v>3812</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3818</v>
+        <v>3822</v>
       </c>
       <c r="B16" t="s">
-        <v>3819</v>
+        <v>3823</v>
       </c>
       <c r="C16" t="s">
         <v>3080</v>
@@ -43397,24 +43470,24 @@
         <v>3081</v>
       </c>
       <c r="F16" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G16" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H16" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I16" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3820</v>
+        <v>3824</v>
       </c>
       <c r="B17" t="s">
-        <v>3821</v>
+        <v>3825</v>
       </c>
       <c r="C17" t="s">
         <v>3080</v>
@@ -43426,24 +43499,24 @@
         <v>3081</v>
       </c>
       <c r="F17" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G17" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H17" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I17" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3822</v>
+        <v>3826</v>
       </c>
       <c r="B18" t="s">
-        <v>3823</v>
+        <v>3827</v>
       </c>
       <c r="C18" t="s">
         <v>3080</v>
@@ -43455,24 +43528,24 @@
         <v>3081</v>
       </c>
       <c r="F18" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G18" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H18" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I18" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3824</v>
+        <v>3828</v>
       </c>
       <c r="B19" t="s">
-        <v>3825</v>
+        <v>3829</v>
       </c>
       <c r="C19" t="s">
         <v>3080</v>
@@ -43484,24 +43557,24 @@
         <v>3081</v>
       </c>
       <c r="F19" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G19" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H19" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I19" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3826</v>
+        <v>3830</v>
       </c>
       <c r="B20" t="s">
-        <v>3827</v>
+        <v>3831</v>
       </c>
       <c r="C20" t="s">
         <v>3080</v>
@@ -43513,24 +43586,24 @@
         <v>3081</v>
       </c>
       <c r="F20" t="s">
-        <v>3828</v>
+        <v>3832</v>
       </c>
       <c r="G20" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H20" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I20" t="s">
-        <v>3829</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3830</v>
+        <v>3834</v>
       </c>
       <c r="B21" t="s">
-        <v>3831</v>
+        <v>3835</v>
       </c>
       <c r="C21" t="s">
         <v>3080</v>
@@ -43542,24 +43615,24 @@
         <v>3081</v>
       </c>
       <c r="F21" t="s">
-        <v>3832</v>
+        <v>3836</v>
       </c>
       <c r="G21" t="s">
-        <v>3833</v>
+        <v>3837</v>
       </c>
       <c r="H21" t="s">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="I21" t="s">
-        <v>3835</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3836</v>
+        <v>3840</v>
       </c>
       <c r="B22" t="s">
-        <v>3837</v>
+        <v>3841</v>
       </c>
       <c r="C22" t="s">
         <v>3080</v>
@@ -43571,24 +43644,24 @@
         <v>3081</v>
       </c>
       <c r="F22" t="s">
+        <v>3842</v>
+      </c>
+      <c r="G22" t="s">
+        <v>3837</v>
+      </c>
+      <c r="H22" t="s">
         <v>3838</v>
       </c>
-      <c r="G22" t="s">
-        <v>3833</v>
-      </c>
-      <c r="H22" t="s">
-        <v>3834</v>
-      </c>
       <c r="I22" t="s">
-        <v>3839</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3840</v>
+        <v>3844</v>
       </c>
       <c r="B23" t="s">
-        <v>3841</v>
+        <v>3845</v>
       </c>
       <c r="C23" t="s">
         <v>3080</v>
@@ -43600,24 +43673,24 @@
         <v>3081</v>
       </c>
       <c r="F23" t="s">
+        <v>3809</v>
+      </c>
+      <c r="G23" t="s">
+        <v>3804</v>
+      </c>
+      <c r="H23" t="s">
         <v>3805</v>
       </c>
-      <c r="G23" t="s">
-        <v>3800</v>
-      </c>
-      <c r="H23" t="s">
-        <v>3801</v>
-      </c>
       <c r="I23" t="s">
-        <v>3815</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3842</v>
+        <v>3846</v>
       </c>
       <c r="B24" t="s">
-        <v>3843</v>
+        <v>3847</v>
       </c>
       <c r="C24" t="s">
         <v>3066</v>
@@ -43629,24 +43702,24 @@
         <v>3070</v>
       </c>
       <c r="F24" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G24" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H24" t="s">
-        <v>3845</v>
+        <v>3849</v>
       </c>
       <c r="I24" t="s">
-        <v>3846</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3847</v>
+        <v>3851</v>
       </c>
       <c r="B25" t="s">
-        <v>3848</v>
+        <v>3852</v>
       </c>
       <c r="C25" t="s">
         <v>3080</v>
@@ -43658,24 +43731,24 @@
         <v>3081</v>
       </c>
       <c r="F25" t="s">
+        <v>3853</v>
+      </c>
+      <c r="G25" t="s">
+        <v>3780</v>
+      </c>
+      <c r="H25" t="s">
         <v>3849</v>
       </c>
-      <c r="G25" t="s">
-        <v>3776</v>
-      </c>
-      <c r="H25" t="s">
-        <v>3845</v>
-      </c>
       <c r="I25" t="s">
-        <v>3850</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3851</v>
+        <v>3855</v>
       </c>
       <c r="B26" t="s">
-        <v>3852</v>
+        <v>3856</v>
       </c>
       <c r="C26" t="s">
         <v>3066</v>
@@ -43687,24 +43760,24 @@
         <v>3070</v>
       </c>
       <c r="F26" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G26" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H26" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I26" t="s">
-        <v>3854</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3855</v>
+        <v>3859</v>
       </c>
       <c r="B27" t="s">
-        <v>3856</v>
+        <v>3860</v>
       </c>
       <c r="C27" t="s">
         <v>3066</v>
@@ -43716,24 +43789,24 @@
         <v>3070</v>
       </c>
       <c r="F27" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G27" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H27" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="I27" t="s">
-        <v>3857</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3858</v>
+        <v>3862</v>
       </c>
       <c r="B28" t="s">
-        <v>3859</v>
+        <v>3863</v>
       </c>
       <c r="C28" t="s">
         <v>3066</v>
@@ -43745,24 +43818,24 @@
         <v>3070</v>
       </c>
       <c r="F28" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G28" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H28" t="s">
-        <v>3860</v>
+        <v>3864</v>
       </c>
       <c r="I28" t="s">
-        <v>3846</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3861</v>
+        <v>3865</v>
       </c>
       <c r="B29" t="s">
-        <v>3862</v>
+        <v>3866</v>
       </c>
       <c r="C29" t="s">
         <v>3080</v>
@@ -43774,24 +43847,24 @@
         <v>3081</v>
       </c>
       <c r="F29" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G29" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H29" t="s">
-        <v>3860</v>
+        <v>3864</v>
       </c>
       <c r="I29" t="s">
-        <v>3850</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3863</v>
+        <v>3867</v>
       </c>
       <c r="B30" t="s">
-        <v>3864</v>
+        <v>3868</v>
       </c>
       <c r="C30" t="s">
         <v>3066</v>
@@ -43803,24 +43876,24 @@
         <v>3070</v>
       </c>
       <c r="F30" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G30" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H30" t="s">
-        <v>3865</v>
+        <v>3869</v>
       </c>
       <c r="I30" t="s">
-        <v>3866</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3867</v>
+        <v>3871</v>
       </c>
       <c r="B31" t="s">
-        <v>3868</v>
+        <v>3872</v>
       </c>
       <c r="C31" t="s">
         <v>3066</v>
@@ -43832,24 +43905,24 @@
         <v>3070</v>
       </c>
       <c r="F31" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G31" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H31" t="s">
-        <v>3865</v>
+        <v>3869</v>
       </c>
       <c r="I31" t="s">
-        <v>3869</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3870</v>
+        <v>3874</v>
       </c>
       <c r="B32" t="s">
-        <v>3871</v>
+        <v>3875</v>
       </c>
       <c r="C32" t="s">
         <v>3066</v>
@@ -43861,24 +43934,24 @@
         <v>3070</v>
       </c>
       <c r="F32" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G32" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H32" t="s">
-        <v>3872</v>
+        <v>3876</v>
       </c>
       <c r="I32" t="s">
-        <v>3846</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3873</v>
+        <v>3877</v>
       </c>
       <c r="B33" t="s">
-        <v>3874</v>
+        <v>3878</v>
       </c>
       <c r="C33" t="s">
         <v>3066</v>
@@ -43890,24 +43963,24 @@
         <v>3070</v>
       </c>
       <c r="F33" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G33" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H33" t="s">
-        <v>3872</v>
+        <v>3876</v>
       </c>
       <c r="I33" t="s">
-        <v>3850</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3875</v>
+        <v>3879</v>
       </c>
       <c r="B34" t="s">
-        <v>3876</v>
+        <v>3880</v>
       </c>
       <c r="C34" t="s">
         <v>3066</v>
@@ -43919,24 +43992,24 @@
         <v>3070</v>
       </c>
       <c r="F34" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G34" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H34" t="s">
-        <v>3877</v>
+        <v>3881</v>
       </c>
       <c r="I34" t="s">
-        <v>3878</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3879</v>
+        <v>3883</v>
       </c>
       <c r="B35" t="s">
-        <v>3880</v>
+        <v>3884</v>
       </c>
       <c r="C35" t="s">
         <v>3066</v>
@@ -43948,24 +44021,24 @@
         <v>3070</v>
       </c>
       <c r="F35" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G35" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H35" t="s">
-        <v>3877</v>
+        <v>3881</v>
       </c>
       <c r="I35" t="s">
-        <v>3881</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3882</v>
+        <v>3886</v>
       </c>
       <c r="B36" t="s">
-        <v>3883</v>
+        <v>3887</v>
       </c>
       <c r="C36" t="s">
         <v>3066</v>
@@ -43977,24 +44050,24 @@
         <v>3070</v>
       </c>
       <c r="F36" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G36" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H36" t="s">
-        <v>3884</v>
+        <v>3888</v>
       </c>
       <c r="I36" t="s">
-        <v>3878</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3885</v>
+        <v>3889</v>
       </c>
       <c r="B37" t="s">
-        <v>3886</v>
+        <v>3890</v>
       </c>
       <c r="C37" t="s">
         <v>3066</v>
@@ -44006,24 +44079,24 @@
         <v>3070</v>
       </c>
       <c r="F37" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G37" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H37" t="s">
-        <v>3884</v>
+        <v>3888</v>
       </c>
       <c r="I37" t="s">
-        <v>3881</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3887</v>
+        <v>3891</v>
       </c>
       <c r="B38" t="s">
-        <v>3888</v>
+        <v>3892</v>
       </c>
       <c r="C38" t="s">
         <v>3066</v>
@@ -44035,24 +44108,24 @@
         <v>3070</v>
       </c>
       <c r="F38" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G38" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H38" t="s">
-        <v>3889</v>
+        <v>3893</v>
       </c>
       <c r="I38" t="s">
-        <v>3846</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3890</v>
+        <v>3894</v>
       </c>
       <c r="B39" t="s">
-        <v>3891</v>
+        <v>3895</v>
       </c>
       <c r="C39" t="s">
         <v>3066</v>
@@ -44064,24 +44137,24 @@
         <v>3070</v>
       </c>
       <c r="F39" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G39" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H39" t="s">
-        <v>3889</v>
+        <v>3893</v>
       </c>
       <c r="I39" t="s">
-        <v>3850</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3892</v>
+        <v>3896</v>
       </c>
       <c r="B40" t="s">
-        <v>3893</v>
+        <v>3897</v>
       </c>
       <c r="C40" t="s">
         <v>3066</v>
@@ -44093,24 +44166,24 @@
         <v>3070</v>
       </c>
       <c r="F40" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="G40" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H40" t="s">
-        <v>3894</v>
+        <v>3898</v>
       </c>
       <c r="I40" t="s">
-        <v>3895</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3896</v>
+        <v>3900</v>
       </c>
       <c r="B41" t="s">
-        <v>3897</v>
+        <v>3901</v>
       </c>
       <c r="C41" t="s">
         <v>3066</v>
@@ -44122,21 +44195,21 @@
         <v>3070</v>
       </c>
       <c r="F41" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="G41" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H41" t="s">
-        <v>3894</v>
+        <v>3898</v>
       </c>
       <c r="I41" t="s">
-        <v>3898</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3899</v>
+        <v>3903</v>
       </c>
       <c r="B42" t="s">
         <v>3296</v>
@@ -44151,24 +44224,24 @@
         <v>3081</v>
       </c>
       <c r="F42" t="s">
-        <v>3900</v>
+        <v>3904</v>
       </c>
       <c r="G42" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H42" t="s">
         <v>3096</v>
       </c>
       <c r="I42" t="s">
-        <v>3901</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3902</v>
+        <v>3906</v>
       </c>
       <c r="B43" t="s">
-        <v>3903</v>
+        <v>3907</v>
       </c>
       <c r="C43" t="s">
         <v>3080</v>
@@ -44180,21 +44253,21 @@
         <v>3081</v>
       </c>
       <c r="F43" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G43" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H43" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I43" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3904</v>
+        <v>3908</v>
       </c>
       <c r="B44" t="s">
         <v>3509</v>
@@ -44209,21 +44282,21 @@
         <v>3070</v>
       </c>
       <c r="F44" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G44" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H44" t="s">
         <v>3096</v>
       </c>
       <c r="I44" t="s">
-        <v>3906</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3907</v>
+        <v>3911</v>
       </c>
       <c r="B45" t="s">
         <v>3297</v>
@@ -44238,21 +44311,21 @@
         <v>3070</v>
       </c>
       <c r="F45" t="s">
-        <v>3908</v>
+        <v>3912</v>
       </c>
       <c r="G45" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H45" t="s">
         <v>3096</v>
       </c>
       <c r="I45" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3909</v>
+        <v>3913</v>
       </c>
       <c r="B46" t="s">
         <v>3519</v>
@@ -44267,24 +44340,24 @@
         <v>3070</v>
       </c>
       <c r="F46" t="s">
-        <v>3828</v>
+        <v>3832</v>
       </c>
       <c r="G46" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H46" t="s">
         <v>3096</v>
       </c>
       <c r="I46" t="s">
-        <v>3829</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3910</v>
+        <v>3914</v>
       </c>
       <c r="B47" t="s">
-        <v>3911</v>
+        <v>3915</v>
       </c>
       <c r="C47" t="s">
         <v>3066</v>
@@ -44296,24 +44369,24 @@
         <v>3070</v>
       </c>
       <c r="F47" t="s">
-        <v>3912</v>
+        <v>3916</v>
       </c>
       <c r="G47" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H47" t="s">
         <v>3096</v>
       </c>
       <c r="I47" t="s">
-        <v>3913</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3914</v>
+        <v>3918</v>
       </c>
       <c r="B48" t="s">
-        <v>3915</v>
+        <v>3919</v>
       </c>
       <c r="C48" t="s">
         <v>3066</v>
@@ -44325,24 +44398,24 @@
         <v>3070</v>
       </c>
       <c r="F48" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G48" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H48" t="s">
         <v>3096</v>
       </c>
       <c r="I48" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3916</v>
+        <v>3920</v>
       </c>
       <c r="B49" t="s">
-        <v>3917</v>
+        <v>3921</v>
       </c>
       <c r="C49" t="s">
         <v>3080</v>
@@ -44354,21 +44427,21 @@
         <v>3081</v>
       </c>
       <c r="F49" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G49" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H49" t="s">
         <v>3096</v>
       </c>
       <c r="I49" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3918</v>
+        <v>3922</v>
       </c>
       <c r="B50" t="s">
         <v>3334</v>
@@ -44383,21 +44456,21 @@
         <v>3081</v>
       </c>
       <c r="F50" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G50" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H50" t="s">
         <v>3096</v>
       </c>
       <c r="I50" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3919</v>
+        <v>3923</v>
       </c>
       <c r="B51" t="s">
         <v>3335</v>
@@ -44412,21 +44485,21 @@
         <v>3081</v>
       </c>
       <c r="F51" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G51" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H51" t="s">
         <v>3096</v>
       </c>
       <c r="I51" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3920</v>
+        <v>3924</v>
       </c>
       <c r="B52" t="s">
         <v>3301</v>
@@ -44441,24 +44514,24 @@
         <v>3081</v>
       </c>
       <c r="F52" t="s">
-        <v>3900</v>
+        <v>3904</v>
       </c>
       <c r="G52" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H52" t="s">
         <v>3094</v>
       </c>
       <c r="I52" t="s">
-        <v>3921</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3922</v>
+        <v>3926</v>
       </c>
       <c r="B53" t="s">
-        <v>3923</v>
+        <v>3927</v>
       </c>
       <c r="C53" t="s">
         <v>3080</v>
@@ -44470,24 +44543,24 @@
         <v>3081</v>
       </c>
       <c r="F53" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G53" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H53" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I53" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3924</v>
+        <v>3928</v>
       </c>
       <c r="B54" t="s">
-        <v>3925</v>
+        <v>3929</v>
       </c>
       <c r="C54" t="s">
         <v>3080</v>
@@ -44499,24 +44572,24 @@
         <v>3081</v>
       </c>
       <c r="F54" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G54" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H54" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I54" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3926</v>
+        <v>3930</v>
       </c>
       <c r="B55" t="s">
-        <v>3927</v>
+        <v>3931</v>
       </c>
       <c r="C55" t="s">
         <v>3080</v>
@@ -44528,21 +44601,21 @@
         <v>3081</v>
       </c>
       <c r="F55" t="s">
-        <v>3928</v>
+        <v>3932</v>
       </c>
       <c r="G55" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H55" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="I55" t="s">
-        <v>3929</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3930</v>
+        <v>3934</v>
       </c>
       <c r="B56" t="s">
         <v>3314</v>
@@ -44557,21 +44630,21 @@
         <v>3081</v>
       </c>
       <c r="F56" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G56" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H56" t="s">
         <v>3094</v>
       </c>
       <c r="I56" t="s">
-        <v>3931</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3932</v>
+        <v>3936</v>
       </c>
       <c r="B57" t="s">
         <v>3302</v>
@@ -44586,21 +44659,21 @@
         <v>3081</v>
       </c>
       <c r="F57" t="s">
-        <v>3908</v>
+        <v>3912</v>
       </c>
       <c r="G57" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H57" t="s">
         <v>3094</v>
       </c>
       <c r="I57" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3934</v>
+        <v>3938</v>
       </c>
       <c r="B58" t="s">
         <v>3381</v>
@@ -44615,24 +44688,24 @@
         <v>3081</v>
       </c>
       <c r="F58" t="s">
-        <v>3787</v>
+        <v>3791</v>
       </c>
       <c r="G58" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H58" t="s">
         <v>3094</v>
       </c>
       <c r="I58" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3935</v>
+        <v>3939</v>
       </c>
       <c r="B59" t="s">
-        <v>3936</v>
+        <v>3940</v>
       </c>
       <c r="C59" t="s">
         <v>3080</v>
@@ -44644,24 +44717,24 @@
         <v>3081</v>
       </c>
       <c r="F59" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G59" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H59" t="s">
         <v>3094</v>
       </c>
       <c r="I59" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3937</v>
+        <v>3941</v>
       </c>
       <c r="B60" t="s">
-        <v>3938</v>
+        <v>3942</v>
       </c>
       <c r="C60" t="s">
         <v>3080</v>
@@ -44673,21 +44746,21 @@
         <v>3081</v>
       </c>
       <c r="F60" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G60" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H60" t="s">
         <v>3094</v>
       </c>
       <c r="I60" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3939</v>
+        <v>3943</v>
       </c>
       <c r="B61" t="s">
         <v>3385</v>
@@ -44702,21 +44775,21 @@
         <v>3081</v>
       </c>
       <c r="F61" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G61" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H61" t="s">
         <v>3094</v>
       </c>
       <c r="I61" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3940</v>
+        <v>3944</v>
       </c>
       <c r="B62" t="s">
         <v>3386</v>
@@ -44731,21 +44804,21 @@
         <v>3081</v>
       </c>
       <c r="F62" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G62" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H62" t="s">
         <v>3094</v>
       </c>
       <c r="I62" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3941</v>
+        <v>3945</v>
       </c>
       <c r="B63" t="s">
         <v>3338</v>
@@ -44760,21 +44833,21 @@
         <v>3081</v>
       </c>
       <c r="F63" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G63" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H63" t="s">
         <v>3096</v>
       </c>
       <c r="I63" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3942</v>
+        <v>3946</v>
       </c>
       <c r="B64" t="s">
         <v>3561</v>
@@ -44789,21 +44862,21 @@
         <v>3081</v>
       </c>
       <c r="F64" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G64" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H64" t="s">
         <v>3094</v>
       </c>
       <c r="I64" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3943</v>
+        <v>3947</v>
       </c>
       <c r="B65" t="s">
         <v>3303</v>
@@ -44818,21 +44891,21 @@
         <v>3081</v>
       </c>
       <c r="F65" t="s">
-        <v>3900</v>
+        <v>3904</v>
       </c>
       <c r="G65" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H65" t="s">
         <v>3092</v>
       </c>
       <c r="I65" t="s">
-        <v>3901</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3944</v>
+        <v>3948</v>
       </c>
       <c r="B66" t="s">
         <v>3316</v>
@@ -44847,21 +44920,21 @@
         <v>3070</v>
       </c>
       <c r="F66" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G66" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H66" t="s">
         <v>3092</v>
       </c>
       <c r="I66" t="s">
-        <v>3906</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3945</v>
+        <v>3949</v>
       </c>
       <c r="B67" t="s">
         <v>3304</v>
@@ -44876,21 +44949,21 @@
         <v>3070</v>
       </c>
       <c r="F67" t="s">
-        <v>3908</v>
+        <v>3912</v>
       </c>
       <c r="G67" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H67" t="s">
         <v>3092</v>
       </c>
       <c r="I67" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3946</v>
+        <v>3950</v>
       </c>
       <c r="B68" t="s">
         <v>3434</v>
@@ -44905,21 +44978,21 @@
         <v>3070</v>
       </c>
       <c r="F68" t="s">
-        <v>3787</v>
+        <v>3791</v>
       </c>
       <c r="G68" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H68" t="s">
         <v>3092</v>
       </c>
       <c r="I68" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3947</v>
+        <v>3951</v>
       </c>
       <c r="B69" t="s">
         <v>3571</v>
@@ -44934,21 +45007,21 @@
         <v>3070</v>
       </c>
       <c r="F69" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G69" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H69" t="s">
         <v>3094</v>
       </c>
       <c r="I69" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3949</v>
+        <v>3953</v>
       </c>
       <c r="B70" t="s">
         <v>3394</v>
@@ -44963,21 +45036,21 @@
         <v>3070</v>
       </c>
       <c r="F70" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G70" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H70" t="s">
         <v>3094</v>
       </c>
       <c r="I70" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3950</v>
+        <v>3954</v>
       </c>
       <c r="B71" t="s">
         <v>3395</v>
@@ -44992,21 +45065,21 @@
         <v>3070</v>
       </c>
       <c r="F71" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G71" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H71" t="s">
         <v>3094</v>
       </c>
       <c r="I71" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3951</v>
+        <v>3955</v>
       </c>
       <c r="B72" t="s">
         <v>3398</v>
@@ -45021,21 +45094,21 @@
         <v>3070</v>
       </c>
       <c r="F72" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G72" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H72" t="s">
         <v>3094</v>
       </c>
       <c r="I72" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3952</v>
+        <v>3956</v>
       </c>
       <c r="B73" t="s">
         <v>3341</v>
@@ -45050,21 +45123,21 @@
         <v>3070</v>
       </c>
       <c r="F73" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G73" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H73" t="s">
         <v>3096</v>
       </c>
       <c r="I73" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3953</v>
+        <v>3957</v>
       </c>
       <c r="B74" t="s">
         <v>3347</v>
@@ -45079,21 +45152,21 @@
         <v>3070</v>
       </c>
       <c r="F74" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G74" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H74" t="s">
         <v>3096</v>
       </c>
       <c r="I74" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3954</v>
+        <v>3958</v>
       </c>
       <c r="B75" t="s">
         <v>3590</v>
@@ -45108,21 +45181,21 @@
         <v>3070</v>
       </c>
       <c r="F75" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G75" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H75" t="s">
         <v>3096</v>
       </c>
       <c r="I75" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3955</v>
+        <v>3959</v>
       </c>
       <c r="B76" t="s">
         <v>3348</v>
@@ -45137,21 +45210,21 @@
         <v>3081</v>
       </c>
       <c r="F76" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G76" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H76" t="s">
         <v>3096</v>
       </c>
       <c r="I76" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3956</v>
+        <v>3960</v>
       </c>
       <c r="B77" t="s">
         <v>3401</v>
@@ -45166,24 +45239,24 @@
         <v>3081</v>
       </c>
       <c r="F77" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G77" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H77" t="s">
         <v>3094</v>
       </c>
       <c r="I77" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="B78" t="s">
-        <v>3958</v>
+        <v>3962</v>
       </c>
       <c r="C78" t="s">
         <v>3080</v>
@@ -45195,21 +45268,21 @@
         <v>3081</v>
       </c>
       <c r="F78" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G78" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H78" t="s">
         <v>3092</v>
       </c>
       <c r="I78" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3959</v>
+        <v>3963</v>
       </c>
       <c r="B79" t="s">
         <v>3432</v>
@@ -45224,21 +45297,21 @@
         <v>3081</v>
       </c>
       <c r="F79" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G79" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H79" t="s">
         <v>3092</v>
       </c>
       <c r="I79" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3960</v>
+        <v>3964</v>
       </c>
       <c r="B80" t="s">
         <v>3437</v>
@@ -45253,21 +45326,21 @@
         <v>3081</v>
       </c>
       <c r="F80" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G80" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H80" t="s">
         <v>3092</v>
       </c>
       <c r="I80" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3961</v>
+        <v>3965</v>
       </c>
       <c r="B81" t="s">
         <v>3404</v>
@@ -45282,24 +45355,24 @@
         <v>3081</v>
       </c>
       <c r="F81" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G81" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H81" t="s">
         <v>3094</v>
       </c>
       <c r="I81" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3962</v>
+        <v>3966</v>
       </c>
       <c r="B82" t="s">
-        <v>3963</v>
+        <v>3967</v>
       </c>
       <c r="C82" t="s">
         <v>3066</v>
@@ -45311,21 +45384,21 @@
         <v>3070</v>
       </c>
       <c r="F82" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G82" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H82" t="s">
         <v>3096</v>
       </c>
       <c r="I82" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3964</v>
+        <v>3968</v>
       </c>
       <c r="B83" t="s">
         <v>3406</v>
@@ -45340,21 +45413,21 @@
         <v>3081</v>
       </c>
       <c r="F83" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G83" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H83" t="s">
         <v>3094</v>
       </c>
       <c r="I83" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3965</v>
+        <v>3969</v>
       </c>
       <c r="B84" t="s">
         <v>3354</v>
@@ -45369,21 +45442,21 @@
         <v>3081</v>
       </c>
       <c r="F84" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G84" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H84" t="s">
         <v>3096</v>
       </c>
       <c r="I84" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3966</v>
+        <v>3970</v>
       </c>
       <c r="B85" t="s">
         <v>3357</v>
@@ -45398,24 +45471,24 @@
         <v>3081</v>
       </c>
       <c r="F85" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G85" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H85" t="s">
         <v>3096</v>
       </c>
       <c r="I85" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3967</v>
+        <v>3971</v>
       </c>
       <c r="B86" t="s">
-        <v>3968</v>
+        <v>3972</v>
       </c>
       <c r="C86" t="s">
         <v>3066</v>
@@ -45427,21 +45500,21 @@
         <v>3070</v>
       </c>
       <c r="F86" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G86" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H86" t="s">
         <v>3096</v>
       </c>
       <c r="I86" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>3969</v>
+        <v>3973</v>
       </c>
       <c r="B87" t="s">
         <v>3625</v>
@@ -45456,24 +45529,24 @@
         <v>3070</v>
       </c>
       <c r="F87" t="s">
-        <v>3787</v>
+        <v>3791</v>
       </c>
       <c r="G87" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H87" t="s">
         <v>3096</v>
       </c>
       <c r="I87" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>3970</v>
+        <v>3974</v>
       </c>
       <c r="B88" t="s">
-        <v>3971</v>
+        <v>3975</v>
       </c>
       <c r="C88" t="s">
         <v>3066</v>
@@ -45485,21 +45558,21 @@
         <v>3070</v>
       </c>
       <c r="F88" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G88" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H88" t="s">
         <v>3096</v>
       </c>
       <c r="I88" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3972</v>
+        <v>3976</v>
       </c>
       <c r="B89" t="s">
         <v>3363</v>
@@ -45514,24 +45587,24 @@
         <v>3070</v>
       </c>
       <c r="F89" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G89" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H89" t="s">
         <v>3096</v>
       </c>
       <c r="I89" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>3973</v>
+        <v>3977</v>
       </c>
       <c r="B90" t="s">
-        <v>3974</v>
+        <v>3978</v>
       </c>
       <c r="C90" t="s">
         <v>3066</v>
@@ -45543,21 +45616,21 @@
         <v>3070</v>
       </c>
       <c r="F90" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G90" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H90" t="s">
         <v>3096</v>
       </c>
       <c r="I90" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>3975</v>
+        <v>3979</v>
       </c>
       <c r="B91" t="s">
         <v>3633</v>
@@ -45572,21 +45645,21 @@
         <v>3070</v>
       </c>
       <c r="F91" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G91" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H91" t="s">
         <v>3096</v>
       </c>
       <c r="I91" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>3976</v>
+        <v>3980</v>
       </c>
       <c r="B92" t="s">
         <v>3635</v>
@@ -45601,21 +45674,21 @@
         <v>3070</v>
       </c>
       <c r="F92" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G92" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H92" t="s">
         <v>3096</v>
       </c>
       <c r="I92" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>3977</v>
+        <v>3981</v>
       </c>
       <c r="B93" t="s">
         <v>3638</v>
@@ -45630,21 +45703,21 @@
         <v>3070</v>
       </c>
       <c r="F93" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G93" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H93" t="s">
         <v>3096</v>
       </c>
       <c r="I93" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>3978</v>
+        <v>3982</v>
       </c>
       <c r="B94" t="s">
         <v>3364</v>
@@ -45659,21 +45732,21 @@
         <v>3070</v>
       </c>
       <c r="F94" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G94" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H94" t="s">
         <v>3096</v>
       </c>
       <c r="I94" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>3979</v>
+        <v>3983</v>
       </c>
       <c r="B95" t="s">
         <v>3367</v>
@@ -45688,21 +45761,21 @@
         <v>3070</v>
       </c>
       <c r="F95" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G95" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H95" t="s">
         <v>3096</v>
       </c>
       <c r="I95" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>3980</v>
+        <v>3984</v>
       </c>
       <c r="B96" t="s">
         <v>3649</v>
@@ -45717,21 +45790,21 @@
         <v>3070</v>
       </c>
       <c r="F96" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G96" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H96" t="s">
         <v>3094</v>
       </c>
       <c r="I96" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>3981</v>
+        <v>3985</v>
       </c>
       <c r="B97" t="s">
         <v>3651</v>
@@ -45746,21 +45819,21 @@
         <v>3070</v>
       </c>
       <c r="F97" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G97" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H97" t="s">
         <v>3096</v>
       </c>
       <c r="I97" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>3982</v>
+        <v>3986</v>
       </c>
       <c r="B98" t="s">
         <v>3655</v>
@@ -45775,21 +45848,21 @@
         <v>3070</v>
       </c>
       <c r="F98" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G98" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H98" t="s">
         <v>3092</v>
       </c>
       <c r="I98" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>3983</v>
+        <v>3987</v>
       </c>
       <c r="B99" t="s">
         <v>3657</v>
@@ -45804,24 +45877,24 @@
         <v>3070</v>
       </c>
       <c r="F99" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G99" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H99" t="s">
         <v>3092</v>
       </c>
       <c r="I99" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>3984</v>
+        <v>3988</v>
       </c>
       <c r="B100" t="s">
-        <v>3985</v>
+        <v>3989</v>
       </c>
       <c r="C100" t="s">
         <v>3066</v>
@@ -45833,21 +45906,21 @@
         <v>3070</v>
       </c>
       <c r="F100" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G100" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H100" t="s">
         <v>3096</v>
       </c>
       <c r="I100" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>3986</v>
+        <v>3990</v>
       </c>
       <c r="B101" t="s">
         <v>3663</v>
@@ -45862,21 +45935,21 @@
         <v>3070</v>
       </c>
       <c r="F101" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G101" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H101" t="s">
         <v>3092</v>
       </c>
       <c r="I101" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>3987</v>
+        <v>3991</v>
       </c>
       <c r="B102" t="s">
         <v>3665</v>
@@ -45891,24 +45964,24 @@
         <v>3070</v>
       </c>
       <c r="F102" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G102" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H102" t="s">
         <v>3092</v>
       </c>
       <c r="I102" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>3988</v>
+        <v>3992</v>
       </c>
       <c r="B103" t="s">
-        <v>3989</v>
+        <v>3993</v>
       </c>
       <c r="C103" t="s">
         <v>3066</v>
@@ -45920,21 +45993,21 @@
         <v>3070</v>
       </c>
       <c r="F103" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G103" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H103" t="s">
         <v>3092</v>
       </c>
       <c r="I103" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>3990</v>
+        <v>3994</v>
       </c>
       <c r="B104" t="s">
         <v>3669</v>
@@ -45949,21 +46022,21 @@
         <v>3070</v>
       </c>
       <c r="F104" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G104" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H104" t="s">
         <v>3092</v>
       </c>
       <c r="I104" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>3991</v>
+        <v>3995</v>
       </c>
       <c r="B105" t="s">
         <v>3671</v>
@@ -45978,21 +46051,21 @@
         <v>3070</v>
       </c>
       <c r="F105" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G105" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H105" t="s">
         <v>3092</v>
       </c>
       <c r="I105" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>3992</v>
+        <v>3996</v>
       </c>
       <c r="B106" t="s">
         <v>3673</v>
@@ -46007,24 +46080,24 @@
         <v>3070</v>
       </c>
       <c r="F106" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G106" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H106" t="s">
         <v>3092</v>
       </c>
       <c r="I106" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>3993</v>
+        <v>3997</v>
       </c>
       <c r="B107" t="s">
-        <v>3994</v>
+        <v>3998</v>
       </c>
       <c r="C107" t="s">
         <v>3066</v>
@@ -46036,21 +46109,21 @@
         <v>3070</v>
       </c>
       <c r="F107" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G107" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H107" t="s">
         <v>3092</v>
       </c>
       <c r="I107" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>3995</v>
+        <v>3999</v>
       </c>
       <c r="B108" t="s">
         <v>3677</v>
@@ -46065,21 +46138,21 @@
         <v>3070</v>
       </c>
       <c r="F108" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G108" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H108" t="s">
         <v>3092</v>
       </c>
       <c r="I108" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>3996</v>
+        <v>4000</v>
       </c>
       <c r="B109" t="s">
         <v>3679</v>
@@ -46094,24 +46167,24 @@
         <v>3070</v>
       </c>
       <c r="F109" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G109" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H109" t="s">
         <v>3092</v>
       </c>
       <c r="I109" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>3997</v>
+        <v>4001</v>
       </c>
       <c r="B110" t="s">
-        <v>3998</v>
+        <v>4002</v>
       </c>
       <c r="C110" t="s">
         <v>3066</v>
@@ -46123,21 +46196,21 @@
         <v>3070</v>
       </c>
       <c r="F110" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G110" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H110" t="s">
         <v>3092</v>
       </c>
       <c r="I110" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3999</v>
+        <v>4003</v>
       </c>
       <c r="B111" t="s">
         <v>3683</v>
@@ -46152,21 +46225,21 @@
         <v>3070</v>
       </c>
       <c r="F111" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G111" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H111" t="s">
         <v>3092</v>
       </c>
       <c r="I111" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>4000</v>
+        <v>4004</v>
       </c>
       <c r="B112" t="s">
         <v>3685</v>
@@ -46181,21 +46254,21 @@
         <v>3070</v>
       </c>
       <c r="F112" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G112" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H112" t="s">
         <v>3092</v>
       </c>
       <c r="I112" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>4001</v>
+        <v>4005</v>
       </c>
       <c r="B113" t="s">
         <v>3687</v>
@@ -46210,21 +46283,21 @@
         <v>3070</v>
       </c>
       <c r="F113" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G113" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H113" t="s">
         <v>3092</v>
       </c>
       <c r="I113" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>4002</v>
+        <v>4006</v>
       </c>
       <c r="B114" t="s">
         <v>3689</v>
@@ -46239,21 +46312,21 @@
         <v>3070</v>
       </c>
       <c r="F114" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G114" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H114" t="s">
         <v>3092</v>
       </c>
       <c r="I114" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="B115" t="s">
         <v>3691</v>
@@ -46268,21 +46341,21 @@
         <v>3070</v>
       </c>
       <c r="F115" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G115" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H115" t="s">
         <v>3092</v>
       </c>
       <c r="I115" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>4004</v>
+        <v>4008</v>
       </c>
       <c r="B116" t="s">
         <v>3443</v>
@@ -46297,21 +46370,21 @@
         <v>3070</v>
       </c>
       <c r="F116" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G116" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H116" t="s">
         <v>3092</v>
       </c>
       <c r="I116" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>4005</v>
+        <v>4009</v>
       </c>
       <c r="B117" t="s">
         <v>3694</v>
@@ -46326,21 +46399,21 @@
         <v>3070</v>
       </c>
       <c r="F117" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G117" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H117" t="s">
         <v>3094</v>
       </c>
       <c r="I117" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="B118" t="s">
         <v>3696</v>
@@ -46355,21 +46428,21 @@
         <v>3070</v>
       </c>
       <c r="F118" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G118" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H118" t="s">
         <v>3094</v>
       </c>
       <c r="I118" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>4007</v>
+        <v>4011</v>
       </c>
       <c r="B119" t="s">
         <v>3698</v>
@@ -46384,21 +46457,21 @@
         <v>3070</v>
       </c>
       <c r="F119" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G119" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H119" t="s">
         <v>3094</v>
       </c>
       <c r="I119" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>4008</v>
+        <v>4012</v>
       </c>
       <c r="B120" t="s">
         <v>3700</v>
@@ -46413,21 +46486,21 @@
         <v>3070</v>
       </c>
       <c r="F120" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G120" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H120" t="s">
         <v>3094</v>
       </c>
       <c r="I120" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>4009</v>
+        <v>4013</v>
       </c>
       <c r="B121" t="s">
         <v>3702</v>
@@ -46442,24 +46515,24 @@
         <v>3070</v>
       </c>
       <c r="F121" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G121" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H121" t="s">
         <v>3094</v>
       </c>
       <c r="I121" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>4010</v>
+        <v>4014</v>
       </c>
       <c r="B122" t="s">
-        <v>4011</v>
+        <v>4015</v>
       </c>
       <c r="C122" t="s">
         <v>3066</v>
@@ -46471,24 +46544,24 @@
         <v>3070</v>
       </c>
       <c r="F122" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G122" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H122" t="s">
         <v>3094</v>
       </c>
       <c r="I122" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>4012</v>
+        <v>4016</v>
       </c>
       <c r="B123" t="s">
-        <v>4013</v>
+        <v>4017</v>
       </c>
       <c r="C123" t="s">
         <v>3066</v>
@@ -46500,21 +46573,21 @@
         <v>3070</v>
       </c>
       <c r="F123" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G123" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H123" t="s">
         <v>3094</v>
       </c>
       <c r="I123" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>4014</v>
+        <v>4018</v>
       </c>
       <c r="B124" t="s">
         <v>3708</v>
@@ -46529,21 +46602,21 @@
         <v>3070</v>
       </c>
       <c r="F124" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G124" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H124" t="s">
         <v>3094</v>
       </c>
       <c r="I124" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>4015</v>
+        <v>4019</v>
       </c>
       <c r="B125" t="s">
         <v>3710</v>
@@ -46558,21 +46631,21 @@
         <v>3070</v>
       </c>
       <c r="F125" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G125" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H125" t="s">
         <v>3094</v>
       </c>
       <c r="I125" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>4016</v>
+        <v>4020</v>
       </c>
       <c r="B126" t="s">
         <v>3712</v>
@@ -46587,21 +46660,21 @@
         <v>3070</v>
       </c>
       <c r="F126" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G126" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H126" t="s">
         <v>3094</v>
       </c>
       <c r="I126" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>4017</v>
+        <v>4021</v>
       </c>
       <c r="B127" t="s">
         <v>3714</v>
@@ -46616,21 +46689,21 @@
         <v>3070</v>
       </c>
       <c r="F127" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G127" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H127" t="s">
         <v>3094</v>
       </c>
       <c r="I127" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>4018</v>
+        <v>4022</v>
       </c>
       <c r="B128" t="s">
         <v>3716</v>
@@ -46645,21 +46718,21 @@
         <v>3070</v>
       </c>
       <c r="F128" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G128" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H128" t="s">
         <v>3094</v>
       </c>
       <c r="I128" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>4019</v>
+        <v>4023</v>
       </c>
       <c r="B129" t="s">
         <v>3446</v>
@@ -46674,21 +46747,21 @@
         <v>3070</v>
       </c>
       <c r="F129" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G129" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H129" t="s">
         <v>3092</v>
       </c>
       <c r="I129" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>4020</v>
+        <v>4024</v>
       </c>
       <c r="B130" t="s">
         <v>3309</v>
@@ -46703,21 +46776,21 @@
         <v>3070</v>
       </c>
       <c r="F130" t="s">
-        <v>3900</v>
+        <v>3904</v>
       </c>
       <c r="G130" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H130" t="s">
         <v>3105</v>
       </c>
       <c r="I130" t="s">
-        <v>4021</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>4022</v>
+        <v>4026</v>
       </c>
       <c r="B131" t="s">
         <v>3325</v>
@@ -46732,24 +46805,24 @@
         <v>3070</v>
       </c>
       <c r="F131" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="G131" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H131" t="s">
         <v>3105</v>
       </c>
       <c r="I131" t="s">
-        <v>4023</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>4024</v>
+        <v>4028</v>
       </c>
       <c r="B132" t="s">
-        <v>4025</v>
+        <v>4029</v>
       </c>
       <c r="C132" t="s">
         <v>3066</v>
@@ -46761,21 +46834,21 @@
         <v>3070</v>
       </c>
       <c r="F132" t="s">
-        <v>3908</v>
+        <v>3912</v>
       </c>
       <c r="G132" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H132" t="s">
         <v>3105</v>
       </c>
       <c r="I132" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>4027</v>
+        <v>4031</v>
       </c>
       <c r="B133" t="s">
         <v>3727</v>
@@ -46790,24 +46863,24 @@
         <v>3070</v>
       </c>
       <c r="F133" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G133" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H133" t="s">
         <v>3105</v>
       </c>
       <c r="I133" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>4028</v>
+        <v>4032</v>
       </c>
       <c r="B134" t="s">
-        <v>4029</v>
+        <v>4033</v>
       </c>
       <c r="C134" t="s">
         <v>3066</v>
@@ -46819,21 +46892,21 @@
         <v>3070</v>
       </c>
       <c r="F134" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G134" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H134" t="s">
         <v>3105</v>
       </c>
       <c r="I134" t="s">
-        <v>4030</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>4031</v>
+        <v>4035</v>
       </c>
       <c r="B135" t="s">
         <v>3733</v>
@@ -46848,21 +46921,21 @@
         <v>3070</v>
       </c>
       <c r="F135" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G135" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H135" t="s">
         <v>3096</v>
       </c>
       <c r="I135" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>4032</v>
+        <v>4036</v>
       </c>
       <c r="B136" t="s">
         <v>3735</v>
@@ -46877,21 +46950,21 @@
         <v>3070</v>
       </c>
       <c r="F136" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G136" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H136" t="s">
         <v>3096</v>
       </c>
       <c r="I136" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>4033</v>
+        <v>4037</v>
       </c>
       <c r="B137" t="s">
         <v>3737</v>
@@ -46906,21 +46979,21 @@
         <v>3070</v>
       </c>
       <c r="F137" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G137" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H137" t="s">
         <v>3096</v>
       </c>
       <c r="I137" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>4034</v>
+        <v>4038</v>
       </c>
       <c r="B138" t="s">
         <v>3739</v>
@@ -46935,21 +47008,21 @@
         <v>3070</v>
       </c>
       <c r="F138" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G138" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H138" t="s">
         <v>3096</v>
       </c>
       <c r="I138" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>4035</v>
+        <v>4039</v>
       </c>
       <c r="B139" t="s">
         <v>3741</v>
@@ -46964,21 +47037,21 @@
         <v>3070</v>
       </c>
       <c r="F139" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G139" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H139" t="s">
         <v>3105</v>
       </c>
       <c r="I139" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>4036</v>
+        <v>4040</v>
       </c>
       <c r="B140" t="s">
         <v>3743</v>
@@ -46993,21 +47066,21 @@
         <v>3070</v>
       </c>
       <c r="F140" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G140" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H140" t="s">
         <v>3105</v>
       </c>
       <c r="I140" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>4037</v>
+        <v>4041</v>
       </c>
       <c r="B141" t="s">
         <v>3747</v>
@@ -47022,21 +47095,21 @@
         <v>3070</v>
       </c>
       <c r="F141" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="G141" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H141" t="s">
         <v>3105</v>
       </c>
       <c r="I141" t="s">
-        <v>4030</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>4038</v>
+        <v>4042</v>
       </c>
       <c r="B142" t="s">
         <v>3749</v>
@@ -47051,21 +47124,21 @@
         <v>3070</v>
       </c>
       <c r="F142" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="G142" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H142" t="s">
         <v>3105</v>
       </c>
       <c r="I142" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>4039</v>
+        <v>4043</v>
       </c>
       <c r="B143" t="s">
         <v>3754</v>
@@ -47080,21 +47153,21 @@
         <v>3070</v>
       </c>
       <c r="F143" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G143" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H143" t="s">
         <v>3105</v>
       </c>
       <c r="I143" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>4040</v>
+        <v>4044</v>
       </c>
       <c r="B144" t="s">
         <v>3756</v>
@@ -47109,21 +47182,21 @@
         <v>3070</v>
       </c>
       <c r="F144" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G144" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H144" t="s">
         <v>3105</v>
       </c>
       <c r="I144" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>4041</v>
+        <v>4045</v>
       </c>
       <c r="B145" t="s">
         <v>3763</v>
@@ -47138,21 +47211,21 @@
         <v>3070</v>
       </c>
       <c r="F145" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G145" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H145" t="s">
         <v>3094</v>
       </c>
       <c r="I145" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>4042</v>
+        <v>4046</v>
       </c>
       <c r="B146" t="s">
         <v>3765</v>
@@ -47167,16 +47240,74 @@
         <v>3070</v>
       </c>
       <c r="F146" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="G146" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="H146" t="s">
         <v>3094</v>
       </c>
       <c r="I146" t="s">
-        <v>3933</v>
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B147" t="s">
+        <v>3769</v>
+      </c>
+      <c r="C147" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D147" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E147" t="s">
+        <v>3070</v>
+      </c>
+      <c r="F147" t="s">
+        <v>3796</v>
+      </c>
+      <c r="G147" t="s">
+        <v>3780</v>
+      </c>
+      <c r="H147" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I147" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>4048</v>
+      </c>
+      <c r="B148" t="s">
+        <v>4049</v>
+      </c>
+      <c r="C148" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D148" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E148" t="s">
+        <v>3070</v>
+      </c>
+      <c r="F148" t="s">
+        <v>3800</v>
+      </c>
+      <c r="G148" t="s">
+        <v>3780</v>
+      </c>
+      <c r="H148" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I148" t="s">
+        <v>3782</v>
       </c>
     </row>
   </sheetData>
